--- a/yontro-sheets/Yontro Content & Uploads.xlsx
+++ b/yontro-sheets/Yontro Content & Uploads.xlsx
@@ -116,7 +116,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">T-YYYYMMDD-PAGE-n, e.g. T-20261027-FT-1</t>
+          <t xml:space="preserve">T-YYYYMMDD-PAGE-n, e.g. T-20261119-FT-1</t>
         </r>
       </text>
     </comment>
@@ -479,7 +479,7 @@
     <t xml:space="preserve">Hook line</t>
   </si>
   <si>
-    <t xml:space="preserve">FT_20261026_1_A</t>
+    <t xml:space="preserve">FT_20261118_1_A</t>
   </si>
   <si>
     <t xml:space="preserve">Posted</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">EXAMPLE: He lost everything at 48</t>
   </si>
   <si>
-    <t xml:space="preserve">T-20261024-FT-1</t>
+    <t xml:space="preserve">T-20261117-FT-1</t>
   </si>
   <si>
     <t xml:space="preserve">Azeem</t>
@@ -656,7 +656,7 @@
     <t xml:space="preserve">Active</t>
   </si>
   <si>
-    <t xml:space="preserve">Week start (Mon)</t>
+    <t xml:space="preserve">Week start</t>
   </si>
   <si>
     <t xml:space="preserve">Week end</t>
@@ -1600,7 +1600,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="n">
-        <v>46321</v>
+        <v>46344</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>31</v>
@@ -1633,7 +1633,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="n">
-        <v>46322</v>
+        <v>46345</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>38</v>
@@ -1658,7 +1658,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="n">
-        <v>46322</v>
+        <v>46345</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>38</v>
@@ -1683,7 +1683,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="n">
-        <v>46322</v>
+        <v>46345</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>38</v>
@@ -1708,7 +1708,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="n">
-        <v>46322</v>
+        <v>46345</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>41</v>
@@ -1733,7 +1733,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="n">
-        <v>46322</v>
+        <v>46345</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>41</v>
@@ -1758,7 +1758,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="n">
-        <v>46322</v>
+        <v>46345</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>41</v>
@@ -1783,7 +1783,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="n">
-        <v>46322</v>
+        <v>46345</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>31</v>
@@ -1808,7 +1808,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="n">
-        <v>46322</v>
+        <v>46345</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>31</v>
@@ -1833,7 +1833,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="n">
-        <v>46322</v>
+        <v>46345</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>31</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="n">
-        <v>46323</v>
+        <v>46346</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>38</v>
@@ -1883,7 +1883,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="n">
-        <v>46323</v>
+        <v>46346</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>38</v>
@@ -1908,7 +1908,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="n">
-        <v>46323</v>
+        <v>46346</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>38</v>
@@ -1933,7 +1933,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="n">
-        <v>46323</v>
+        <v>46346</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>41</v>
@@ -1958,7 +1958,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="n">
-        <v>46323</v>
+        <v>46346</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>41</v>
@@ -1983,7 +1983,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="n">
-        <v>46323</v>
+        <v>46346</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>41</v>
@@ -2008,7 +2008,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="n">
-        <v>46323</v>
+        <v>46346</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>31</v>
@@ -2033,7 +2033,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="n">
-        <v>46323</v>
+        <v>46346</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>31</v>
@@ -2058,7 +2058,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="n">
-        <v>46323</v>
+        <v>46346</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>31</v>
@@ -2083,7 +2083,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="n">
-        <v>46324</v>
+        <v>46347</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>38</v>
@@ -2108,7 +2108,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="n">
-        <v>46324</v>
+        <v>46347</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>38</v>
@@ -2133,7 +2133,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="n">
-        <v>46324</v>
+        <v>46347</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>38</v>
@@ -2158,7 +2158,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="n">
-        <v>46324</v>
+        <v>46347</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>41</v>
@@ -2183,7 +2183,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="n">
-        <v>46324</v>
+        <v>46347</v>
       </c>
       <c r="B25" s="12" t="s">
         <v>41</v>
@@ -2208,7 +2208,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="n">
-        <v>46324</v>
+        <v>46347</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>41</v>
@@ -2233,7 +2233,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="n">
-        <v>46324</v>
+        <v>46347</v>
       </c>
       <c r="B27" s="12" t="s">
         <v>31</v>
@@ -2258,7 +2258,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="n">
-        <v>46324</v>
+        <v>46347</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>31</v>
@@ -2283,7 +2283,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="n">
-        <v>46324</v>
+        <v>46347</v>
       </c>
       <c r="B29" s="12" t="s">
         <v>31</v>
@@ -2308,7 +2308,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="n">
-        <v>46325</v>
+        <v>46348</v>
       </c>
       <c r="B30" s="12" t="s">
         <v>38</v>
@@ -2333,7 +2333,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="n">
-        <v>46325</v>
+        <v>46348</v>
       </c>
       <c r="B31" s="12" t="s">
         <v>38</v>
@@ -2358,7 +2358,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="n">
-        <v>46325</v>
+        <v>46348</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>38</v>
@@ -2383,7 +2383,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="n">
-        <v>46325</v>
+        <v>46348</v>
       </c>
       <c r="B33" s="12" t="s">
         <v>41</v>
@@ -2408,7 +2408,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="n">
-        <v>46325</v>
+        <v>46348</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>41</v>
@@ -2433,7 +2433,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="11" t="n">
-        <v>46325</v>
+        <v>46348</v>
       </c>
       <c r="B35" s="12" t="s">
         <v>41</v>
@@ -2458,7 +2458,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="n">
-        <v>46325</v>
+        <v>46348</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>31</v>
@@ -2483,7 +2483,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="n">
-        <v>46325</v>
+        <v>46348</v>
       </c>
       <c r="B37" s="12" t="s">
         <v>31</v>
@@ -2508,7 +2508,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="n">
-        <v>46325</v>
+        <v>46348</v>
       </c>
       <c r="B38" s="12" t="s">
         <v>31</v>
@@ -2533,7 +2533,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="n">
-        <v>46326</v>
+        <v>46349</v>
       </c>
       <c r="B39" s="12" t="s">
         <v>38</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="n">
-        <v>46326</v>
+        <v>46349</v>
       </c>
       <c r="B40" s="12" t="s">
         <v>38</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="n">
-        <v>46326</v>
+        <v>46349</v>
       </c>
       <c r="B41" s="12" t="s">
         <v>38</v>
@@ -2608,7 +2608,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="11" t="n">
-        <v>46326</v>
+        <v>46349</v>
       </c>
       <c r="B42" s="12" t="s">
         <v>41</v>
@@ -2633,7 +2633,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="11" t="n">
-        <v>46326</v>
+        <v>46349</v>
       </c>
       <c r="B43" s="12" t="s">
         <v>41</v>
@@ -2658,7 +2658,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="11" t="n">
-        <v>46326</v>
+        <v>46349</v>
       </c>
       <c r="B44" s="12" t="s">
         <v>41</v>
@@ -2683,7 +2683,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="11" t="n">
-        <v>46326</v>
+        <v>46349</v>
       </c>
       <c r="B45" s="12" t="s">
         <v>31</v>
@@ -2708,7 +2708,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="11" t="n">
-        <v>46326</v>
+        <v>46349</v>
       </c>
       <c r="B46" s="12" t="s">
         <v>31</v>
@@ -2733,7 +2733,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="11" t="n">
-        <v>46326</v>
+        <v>46349</v>
       </c>
       <c r="B47" s="12" t="s">
         <v>31</v>
@@ -2758,7 +2758,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="11" t="n">
-        <v>46327</v>
+        <v>46350</v>
       </c>
       <c r="B48" s="12" t="s">
         <v>38</v>
@@ -2783,7 +2783,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="11" t="n">
-        <v>46327</v>
+        <v>46350</v>
       </c>
       <c r="B49" s="12" t="s">
         <v>38</v>
@@ -2808,7 +2808,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="11" t="n">
-        <v>46327</v>
+        <v>46350</v>
       </c>
       <c r="B50" s="12" t="s">
         <v>38</v>
@@ -2833,7 +2833,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="11" t="n">
-        <v>46327</v>
+        <v>46350</v>
       </c>
       <c r="B51" s="12" t="s">
         <v>41</v>
@@ -2858,7 +2858,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="11" t="n">
-        <v>46327</v>
+        <v>46350</v>
       </c>
       <c r="B52" s="12" t="s">
         <v>41</v>
@@ -2883,7 +2883,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="11" t="n">
-        <v>46327</v>
+        <v>46350</v>
       </c>
       <c r="B53" s="12" t="s">
         <v>41</v>
@@ -2908,7 +2908,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="11" t="n">
-        <v>46327</v>
+        <v>46350</v>
       </c>
       <c r="B54" s="12" t="s">
         <v>31</v>
@@ -2933,7 +2933,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="11" t="n">
-        <v>46327</v>
+        <v>46350</v>
       </c>
       <c r="B55" s="12" t="s">
         <v>31</v>
@@ -2958,7 +2958,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="11" t="n">
-        <v>46327</v>
+        <v>46350</v>
       </c>
       <c r="B56" s="12" t="s">
         <v>31</v>
@@ -2983,7 +2983,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="11" t="n">
-        <v>46328</v>
+        <v>46351</v>
       </c>
       <c r="B57" s="12" t="s">
         <v>38</v>
@@ -3008,7 +3008,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="11" t="n">
-        <v>46328</v>
+        <v>46351</v>
       </c>
       <c r="B58" s="12" t="s">
         <v>38</v>
@@ -3033,7 +3033,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="11" t="n">
-        <v>46328</v>
+        <v>46351</v>
       </c>
       <c r="B59" s="12" t="s">
         <v>38</v>
@@ -3058,7 +3058,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="11" t="n">
-        <v>46328</v>
+        <v>46351</v>
       </c>
       <c r="B60" s="12" t="s">
         <v>41</v>
@@ -3083,7 +3083,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="11" t="n">
-        <v>46328</v>
+        <v>46351</v>
       </c>
       <c r="B61" s="12" t="s">
         <v>41</v>
@@ -3108,7 +3108,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="11" t="n">
-        <v>46328</v>
+        <v>46351</v>
       </c>
       <c r="B62" s="12" t="s">
         <v>41</v>
@@ -3133,7 +3133,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="11" t="n">
-        <v>46328</v>
+        <v>46351</v>
       </c>
       <c r="B63" s="12" t="s">
         <v>31</v>
@@ -3158,7 +3158,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="11" t="n">
-        <v>46328</v>
+        <v>46351</v>
       </c>
       <c r="B64" s="12" t="s">
         <v>31</v>
@@ -3183,7 +3183,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="11" t="n">
-        <v>46328</v>
+        <v>46351</v>
       </c>
       <c r="B65" s="12" t="s">
         <v>31</v>
@@ -3208,7 +3208,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="11" t="n">
-        <v>46329</v>
+        <v>46352</v>
       </c>
       <c r="B66" s="12" t="s">
         <v>38</v>
@@ -3233,7 +3233,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="11" t="n">
-        <v>46329</v>
+        <v>46352</v>
       </c>
       <c r="B67" s="12" t="s">
         <v>38</v>
@@ -3258,7 +3258,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="11" t="n">
-        <v>46329</v>
+        <v>46352</v>
       </c>
       <c r="B68" s="12" t="s">
         <v>38</v>
@@ -3283,7 +3283,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="11" t="n">
-        <v>46329</v>
+        <v>46352</v>
       </c>
       <c r="B69" s="12" t="s">
         <v>41</v>
@@ -3308,7 +3308,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="11" t="n">
-        <v>46329</v>
+        <v>46352</v>
       </c>
       <c r="B70" s="12" t="s">
         <v>41</v>
@@ -3333,7 +3333,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="11" t="n">
-        <v>46329</v>
+        <v>46352</v>
       </c>
       <c r="B71" s="12" t="s">
         <v>41</v>
@@ -3358,7 +3358,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="11" t="n">
-        <v>46329</v>
+        <v>46352</v>
       </c>
       <c r="B72" s="12" t="s">
         <v>31</v>
@@ -3383,7 +3383,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="11" t="n">
-        <v>46329</v>
+        <v>46352</v>
       </c>
       <c r="B73" s="12" t="s">
         <v>31</v>
@@ -3408,7 +3408,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="11" t="n">
-        <v>46329</v>
+        <v>46352</v>
       </c>
       <c r="B74" s="12" t="s">
         <v>31</v>
@@ -3433,7 +3433,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="11" t="n">
-        <v>46330</v>
+        <v>46353</v>
       </c>
       <c r="B75" s="12" t="s">
         <v>38</v>
@@ -3458,7 +3458,7 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="11" t="n">
-        <v>46330</v>
+        <v>46353</v>
       </c>
       <c r="B76" s="12" t="s">
         <v>38</v>
@@ -3483,7 +3483,7 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="11" t="n">
-        <v>46330</v>
+        <v>46353</v>
       </c>
       <c r="B77" s="12" t="s">
         <v>38</v>
@@ -3508,7 +3508,7 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="11" t="n">
-        <v>46330</v>
+        <v>46353</v>
       </c>
       <c r="B78" s="12" t="s">
         <v>41</v>
@@ -3533,7 +3533,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="11" t="n">
-        <v>46330</v>
+        <v>46353</v>
       </c>
       <c r="B79" s="12" t="s">
         <v>41</v>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="11" t="n">
-        <v>46330</v>
+        <v>46353</v>
       </c>
       <c r="B80" s="12" t="s">
         <v>41</v>
@@ -3583,7 +3583,7 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="11" t="n">
-        <v>46330</v>
+        <v>46353</v>
       </c>
       <c r="B81" s="12" t="s">
         <v>31</v>
@@ -3608,7 +3608,7 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="11" t="n">
-        <v>46330</v>
+        <v>46353</v>
       </c>
       <c r="B82" s="12" t="s">
         <v>31</v>
@@ -3633,7 +3633,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="11" t="n">
-        <v>46330</v>
+        <v>46353</v>
       </c>
       <c r="B83" s="12" t="s">
         <v>31</v>
@@ -3658,7 +3658,7 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="11" t="n">
-        <v>46331</v>
+        <v>46354</v>
       </c>
       <c r="B84" s="12" t="s">
         <v>38</v>
@@ -3683,7 +3683,7 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="11" t="n">
-        <v>46331</v>
+        <v>46354</v>
       </c>
       <c r="B85" s="12" t="s">
         <v>38</v>
@@ -3708,7 +3708,7 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="11" t="n">
-        <v>46331</v>
+        <v>46354</v>
       </c>
       <c r="B86" s="12" t="s">
         <v>38</v>
@@ -3733,7 +3733,7 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="11" t="n">
-        <v>46331</v>
+        <v>46354</v>
       </c>
       <c r="B87" s="12" t="s">
         <v>41</v>
@@ -3758,7 +3758,7 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="11" t="n">
-        <v>46331</v>
+        <v>46354</v>
       </c>
       <c r="B88" s="12" t="s">
         <v>41</v>
@@ -3783,7 +3783,7 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="11" t="n">
-        <v>46331</v>
+        <v>46354</v>
       </c>
       <c r="B89" s="12" t="s">
         <v>41</v>
@@ -3808,7 +3808,7 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="11" t="n">
-        <v>46331</v>
+        <v>46354</v>
       </c>
       <c r="B90" s="12" t="s">
         <v>31</v>
@@ -3833,7 +3833,7 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="11" t="n">
-        <v>46331</v>
+        <v>46354</v>
       </c>
       <c r="B91" s="12" t="s">
         <v>31</v>
@@ -3858,7 +3858,7 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="11" t="n">
-        <v>46331</v>
+        <v>46354</v>
       </c>
       <c r="B92" s="12" t="s">
         <v>31</v>
@@ -3883,7 +3883,7 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="11" t="n">
-        <v>46332</v>
+        <v>46355</v>
       </c>
       <c r="B93" s="12" t="s">
         <v>38</v>
@@ -3908,7 +3908,7 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="11" t="n">
-        <v>46332</v>
+        <v>46355</v>
       </c>
       <c r="B94" s="12" t="s">
         <v>38</v>
@@ -3933,7 +3933,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="11" t="n">
-        <v>46332</v>
+        <v>46355</v>
       </c>
       <c r="B95" s="12" t="s">
         <v>38</v>
@@ -3958,7 +3958,7 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="11" t="n">
-        <v>46332</v>
+        <v>46355</v>
       </c>
       <c r="B96" s="12" t="s">
         <v>41</v>
@@ -3983,7 +3983,7 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="11" t="n">
-        <v>46332</v>
+        <v>46355</v>
       </c>
       <c r="B97" s="12" t="s">
         <v>41</v>
@@ -4008,7 +4008,7 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="11" t="n">
-        <v>46332</v>
+        <v>46355</v>
       </c>
       <c r="B98" s="12" t="s">
         <v>41</v>
@@ -4033,7 +4033,7 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="11" t="n">
-        <v>46332</v>
+        <v>46355</v>
       </c>
       <c r="B99" s="12" t="s">
         <v>31</v>
@@ -4058,7 +4058,7 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="11" t="n">
-        <v>46332</v>
+        <v>46355</v>
       </c>
       <c r="B100" s="12" t="s">
         <v>31</v>
@@ -4083,7 +4083,7 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="11" t="n">
-        <v>46332</v>
+        <v>46355</v>
       </c>
       <c r="B101" s="12" t="s">
         <v>31</v>
@@ -4108,7 +4108,7 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="11" t="n">
-        <v>46333</v>
+        <v>46356</v>
       </c>
       <c r="B102" s="12" t="s">
         <v>38</v>
@@ -4133,7 +4133,7 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="11" t="n">
-        <v>46333</v>
+        <v>46356</v>
       </c>
       <c r="B103" s="12" t="s">
         <v>38</v>
@@ -4158,7 +4158,7 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="11" t="n">
-        <v>46333</v>
+        <v>46356</v>
       </c>
       <c r="B104" s="12" t="s">
         <v>38</v>
@@ -4183,7 +4183,7 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="11" t="n">
-        <v>46333</v>
+        <v>46356</v>
       </c>
       <c r="B105" s="12" t="s">
         <v>41</v>
@@ -4208,7 +4208,7 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="11" t="n">
-        <v>46333</v>
+        <v>46356</v>
       </c>
       <c r="B106" s="12" t="s">
         <v>41</v>
@@ -4233,7 +4233,7 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="11" t="n">
-        <v>46333</v>
+        <v>46356</v>
       </c>
       <c r="B107" s="12" t="s">
         <v>41</v>
@@ -4258,7 +4258,7 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="11" t="n">
-        <v>46333</v>
+        <v>46356</v>
       </c>
       <c r="B108" s="12" t="s">
         <v>31</v>
@@ -4283,7 +4283,7 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="11" t="n">
-        <v>46333</v>
+        <v>46356</v>
       </c>
       <c r="B109" s="12" t="s">
         <v>31</v>
@@ -4308,7 +4308,7 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="11" t="n">
-        <v>46333</v>
+        <v>46356</v>
       </c>
       <c r="B110" s="12" t="s">
         <v>31</v>
@@ -4333,7 +4333,7 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="11" t="n">
-        <v>46334</v>
+        <v>46357</v>
       </c>
       <c r="B111" s="12" t="s">
         <v>38</v>
@@ -4358,7 +4358,7 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="11" t="n">
-        <v>46334</v>
+        <v>46357</v>
       </c>
       <c r="B112" s="12" t="s">
         <v>38</v>
@@ -4383,7 +4383,7 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="11" t="n">
-        <v>46334</v>
+        <v>46357</v>
       </c>
       <c r="B113" s="12" t="s">
         <v>38</v>
@@ -4408,7 +4408,7 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="11" t="n">
-        <v>46334</v>
+        <v>46357</v>
       </c>
       <c r="B114" s="12" t="s">
         <v>41</v>
@@ -4433,7 +4433,7 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="11" t="n">
-        <v>46334</v>
+        <v>46357</v>
       </c>
       <c r="B115" s="12" t="s">
         <v>41</v>
@@ -4458,7 +4458,7 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="11" t="n">
-        <v>46334</v>
+        <v>46357</v>
       </c>
       <c r="B116" s="12" t="s">
         <v>41</v>
@@ -4483,7 +4483,7 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="11" t="n">
-        <v>46334</v>
+        <v>46357</v>
       </c>
       <c r="B117" s="12" t="s">
         <v>31</v>
@@ -4508,7 +4508,7 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="11" t="n">
-        <v>46334</v>
+        <v>46357</v>
       </c>
       <c r="B118" s="12" t="s">
         <v>31</v>
@@ -4533,7 +4533,7 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="11" t="n">
-        <v>46334</v>
+        <v>46357</v>
       </c>
       <c r="B119" s="12" t="s">
         <v>31</v>
@@ -4558,7 +4558,7 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="11" t="n">
-        <v>46335</v>
+        <v>46358</v>
       </c>
       <c r="B120" s="12" t="s">
         <v>38</v>
@@ -4583,7 +4583,7 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="11" t="n">
-        <v>46335</v>
+        <v>46358</v>
       </c>
       <c r="B121" s="12" t="s">
         <v>38</v>
@@ -4608,7 +4608,7 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="11" t="n">
-        <v>46335</v>
+        <v>46358</v>
       </c>
       <c r="B122" s="12" t="s">
         <v>38</v>
@@ -4633,7 +4633,7 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="11" t="n">
-        <v>46335</v>
+        <v>46358</v>
       </c>
       <c r="B123" s="12" t="s">
         <v>41</v>
@@ -4658,7 +4658,7 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="11" t="n">
-        <v>46335</v>
+        <v>46358</v>
       </c>
       <c r="B124" s="12" t="s">
         <v>41</v>
@@ -4683,7 +4683,7 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="11" t="n">
-        <v>46335</v>
+        <v>46358</v>
       </c>
       <c r="B125" s="12" t="s">
         <v>41</v>
@@ -4708,7 +4708,7 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="11" t="n">
-        <v>46335</v>
+        <v>46358</v>
       </c>
       <c r="B126" s="12" t="s">
         <v>31</v>
@@ -4733,7 +4733,7 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="11" t="n">
-        <v>46335</v>
+        <v>46358</v>
       </c>
       <c r="B127" s="12" t="s">
         <v>31</v>
@@ -4758,7 +4758,7 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="11" t="n">
-        <v>46335</v>
+        <v>46358</v>
       </c>
       <c r="B128" s="12" t="s">
         <v>31</v>
@@ -4908,7 +4908,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="n">
-        <v>46320</v>
+        <v>46344</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>31</v>
@@ -15067,7 +15067,7 @@
         <v>59</v>
       </c>
       <c r="B2" s="8" t="n">
-        <v>46319</v>
+        <v>46343</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>31</v>
@@ -15125,7 +15125,7 @@
         <v>Yes: add to Constants</v>
       </c>
       <c r="T2" s="8" t="n">
-        <v>46320</v>
+        <v>46344</v>
       </c>
       <c r="U2" s="9"/>
     </row>
@@ -29177,7 +29177,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="8" t="n">
-        <v>46320</v>
+        <v>46344</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>35</v>
@@ -31675,11 +31675,11 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="n">
-        <v>46321</v>
+        <v>46345</v>
       </c>
       <c r="B2" s="22" t="n">
         <f aca="false">IF(A2="","",A2+6)</f>
-        <v>46327</v>
+        <v>46351</v>
       </c>
       <c r="C2" s="12" t="s">
         <v>38</v>
@@ -31731,11 +31731,11 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="n">
-        <v>46321</v>
+        <v>46345</v>
       </c>
       <c r="B3" s="22" t="n">
         <f aca="false">IF(A3="","",A3+6)</f>
-        <v>46327</v>
+        <v>46351</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>41</v>
@@ -31787,11 +31787,11 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="n">
-        <v>46321</v>
+        <v>46345</v>
       </c>
       <c r="B4" s="22" t="n">
         <f aca="false">IF(A4="","",A4+6)</f>
-        <v>46327</v>
+        <v>46351</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>31</v>
@@ -31843,11 +31843,11 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="n">
-        <v>46328</v>
+        <v>46352</v>
       </c>
       <c r="B5" s="22" t="n">
         <f aca="false">IF(A5="","",A5+6)</f>
-        <v>46334</v>
+        <v>46358</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>38</v>
@@ -31899,11 +31899,11 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="n">
-        <v>46328</v>
+        <v>46352</v>
       </c>
       <c r="B6" s="22" t="n">
         <f aca="false">IF(A6="","",A6+6)</f>
-        <v>46334</v>
+        <v>46358</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>41</v>
@@ -31955,11 +31955,11 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="n">
-        <v>46328</v>
+        <v>46352</v>
       </c>
       <c r="B7" s="22" t="n">
         <f aca="false">IF(A7="","",A7+6)</f>
-        <v>46334</v>
+        <v>46358</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>31</v>
@@ -32011,11 +32011,11 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="n">
-        <v>46335</v>
+        <v>46359</v>
       </c>
       <c r="B8" s="22" t="n">
         <f aca="false">IF(A8="","",A8+6)</f>
-        <v>46341</v>
+        <v>46365</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>38</v>
@@ -32067,11 +32067,11 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="n">
-        <v>46335</v>
+        <v>46359</v>
       </c>
       <c r="B9" s="22" t="n">
         <f aca="false">IF(A9="","",A9+6)</f>
-        <v>46341</v>
+        <v>46365</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>41</v>
@@ -32123,11 +32123,11 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="n">
-        <v>46335</v>
+        <v>46359</v>
       </c>
       <c r="B10" s="22" t="n">
         <f aca="false">IF(A10="","",A10+6)</f>
-        <v>46341</v>
+        <v>46365</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>31</v>
@@ -32179,11 +32179,11 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="n">
-        <v>46342</v>
+        <v>46366</v>
       </c>
       <c r="B11" s="22" t="n">
         <f aca="false">IF(A11="","",A11+6)</f>
-        <v>46348</v>
+        <v>46372</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>38</v>
@@ -32235,11 +32235,11 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="n">
-        <v>46342</v>
+        <v>46366</v>
       </c>
       <c r="B12" s="22" t="n">
         <f aca="false">IF(A12="","",A12+6)</f>
-        <v>46348</v>
+        <v>46372</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>41</v>
@@ -32291,11 +32291,11 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="n">
-        <v>46342</v>
+        <v>46366</v>
       </c>
       <c r="B13" s="22" t="n">
         <f aca="false">IF(A13="","",A13+6)</f>
-        <v>46348</v>
+        <v>46372</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>31</v>
@@ -32347,11 +32347,11 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="n">
-        <v>46349</v>
+        <v>46373</v>
       </c>
       <c r="B14" s="22" t="n">
         <f aca="false">IF(A14="","",A14+6)</f>
-        <v>46355</v>
+        <v>46379</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>38</v>
@@ -32403,11 +32403,11 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="n">
-        <v>46349</v>
+        <v>46373</v>
       </c>
       <c r="B15" s="22" t="n">
         <f aca="false">IF(A15="","",A15+6)</f>
-        <v>46355</v>
+        <v>46379</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>41</v>
@@ -32459,11 +32459,11 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="n">
-        <v>46349</v>
+        <v>46373</v>
       </c>
       <c r="B16" s="22" t="n">
         <f aca="false">IF(A16="","",A16+6)</f>
-        <v>46355</v>
+        <v>46379</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>31</v>
@@ -32515,11 +32515,11 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="n">
-        <v>46356</v>
+        <v>46380</v>
       </c>
       <c r="B17" s="22" t="n">
         <f aca="false">IF(A17="","",A17+6)</f>
-        <v>46362</v>
+        <v>46386</v>
       </c>
       <c r="C17" s="12" t="s">
         <v>38</v>
@@ -32571,11 +32571,11 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="n">
-        <v>46356</v>
+        <v>46380</v>
       </c>
       <c r="B18" s="22" t="n">
         <f aca="false">IF(A18="","",A18+6)</f>
-        <v>46362</v>
+        <v>46386</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>41</v>
@@ -32627,11 +32627,11 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="n">
-        <v>46356</v>
+        <v>46380</v>
       </c>
       <c r="B19" s="22" t="n">
         <f aca="false">IF(A19="","",A19+6)</f>
-        <v>46362</v>
+        <v>46386</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>31</v>
@@ -32683,11 +32683,11 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="n">
-        <v>46363</v>
+        <v>46387</v>
       </c>
       <c r="B20" s="22" t="n">
         <f aca="false">IF(A20="","",A20+6)</f>
-        <v>46369</v>
+        <v>46393</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>38</v>
@@ -32739,11 +32739,11 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="n">
-        <v>46363</v>
+        <v>46387</v>
       </c>
       <c r="B21" s="22" t="n">
         <f aca="false">IF(A21="","",A21+6)</f>
-        <v>46369</v>
+        <v>46393</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>41</v>
@@ -32795,11 +32795,11 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="n">
-        <v>46363</v>
+        <v>46387</v>
       </c>
       <c r="B22" s="22" t="n">
         <f aca="false">IF(A22="","",A22+6)</f>
-        <v>46369</v>
+        <v>46393</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>31</v>
@@ -32851,11 +32851,11 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="n">
-        <v>46370</v>
+        <v>46394</v>
       </c>
       <c r="B23" s="22" t="n">
         <f aca="false">IF(A23="","",A23+6)</f>
-        <v>46376</v>
+        <v>46400</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>38</v>
@@ -32907,11 +32907,11 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="n">
-        <v>46370</v>
+        <v>46394</v>
       </c>
       <c r="B24" s="22" t="n">
         <f aca="false">IF(A24="","",A24+6)</f>
-        <v>46376</v>
+        <v>46400</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>41</v>
@@ -32963,11 +32963,11 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="n">
-        <v>46370</v>
+        <v>46394</v>
       </c>
       <c r="B25" s="22" t="n">
         <f aca="false">IF(A25="","",A25+6)</f>
-        <v>46376</v>
+        <v>46400</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>31</v>
@@ -33019,11 +33019,11 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="n">
-        <v>46377</v>
+        <v>46401</v>
       </c>
       <c r="B26" s="22" t="n">
         <f aca="false">IF(A26="","",A26+6)</f>
-        <v>46383</v>
+        <v>46407</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>38</v>
@@ -33075,11 +33075,11 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="n">
-        <v>46377</v>
+        <v>46401</v>
       </c>
       <c r="B27" s="22" t="n">
         <f aca="false">IF(A27="","",A27+6)</f>
-        <v>46383</v>
+        <v>46407</v>
       </c>
       <c r="C27" s="12" t="s">
         <v>41</v>
@@ -33131,11 +33131,11 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="n">
-        <v>46377</v>
+        <v>46401</v>
       </c>
       <c r="B28" s="22" t="n">
         <f aca="false">IF(A28="","",A28+6)</f>
-        <v>46383</v>
+        <v>46407</v>
       </c>
       <c r="C28" s="12" t="s">
         <v>31</v>
@@ -33187,11 +33187,11 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="n">
-        <v>46384</v>
+        <v>46408</v>
       </c>
       <c r="B29" s="22" t="n">
         <f aca="false">IF(A29="","",A29+6)</f>
-        <v>46390</v>
+        <v>46414</v>
       </c>
       <c r="C29" s="12" t="s">
         <v>38</v>
@@ -33243,11 +33243,11 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="n">
-        <v>46384</v>
+        <v>46408</v>
       </c>
       <c r="B30" s="22" t="n">
         <f aca="false">IF(A30="","",A30+6)</f>
-        <v>46390</v>
+        <v>46414</v>
       </c>
       <c r="C30" s="12" t="s">
         <v>41</v>
@@ -33299,11 +33299,11 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="n">
-        <v>46384</v>
+        <v>46408</v>
       </c>
       <c r="B31" s="22" t="n">
         <f aca="false">IF(A31="","",A31+6)</f>
-        <v>46390</v>
+        <v>46414</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>31</v>
@@ -33355,11 +33355,11 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="n">
-        <v>46391</v>
+        <v>46415</v>
       </c>
       <c r="B32" s="22" t="n">
         <f aca="false">IF(A32="","",A32+6)</f>
-        <v>46397</v>
+        <v>46421</v>
       </c>
       <c r="C32" s="12" t="s">
         <v>38</v>
@@ -33411,11 +33411,11 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="n">
-        <v>46391</v>
+        <v>46415</v>
       </c>
       <c r="B33" s="22" t="n">
         <f aca="false">IF(A33="","",A33+6)</f>
-        <v>46397</v>
+        <v>46421</v>
       </c>
       <c r="C33" s="12" t="s">
         <v>41</v>
@@ -33467,11 +33467,11 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="n">
-        <v>46391</v>
+        <v>46415</v>
       </c>
       <c r="B34" s="22" t="n">
         <f aca="false">IF(A34="","",A34+6)</f>
-        <v>46397</v>
+        <v>46421</v>
       </c>
       <c r="C34" s="12" t="s">
         <v>31</v>
@@ -33523,11 +33523,11 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="11" t="n">
-        <v>46398</v>
+        <v>46422</v>
       </c>
       <c r="B35" s="22" t="n">
         <f aca="false">IF(A35="","",A35+6)</f>
-        <v>46404</v>
+        <v>46428</v>
       </c>
       <c r="C35" s="12" t="s">
         <v>38</v>
@@ -33579,11 +33579,11 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="n">
-        <v>46398</v>
+        <v>46422</v>
       </c>
       <c r="B36" s="22" t="n">
         <f aca="false">IF(A36="","",A36+6)</f>
-        <v>46404</v>
+        <v>46428</v>
       </c>
       <c r="C36" s="12" t="s">
         <v>41</v>
@@ -33635,11 +33635,11 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="n">
-        <v>46398</v>
+        <v>46422</v>
       </c>
       <c r="B37" s="22" t="n">
         <f aca="false">IF(A37="","",A37+6)</f>
-        <v>46404</v>
+        <v>46428</v>
       </c>
       <c r="C37" s="12" t="s">
         <v>31</v>
@@ -35016,11 +35016,11 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="n">
-        <v>46321</v>
+        <v>46345</v>
       </c>
       <c r="B2" s="22" t="n">
         <f aca="false">IF(A2="","",A2+6)</f>
-        <v>46327</v>
+        <v>46351</v>
       </c>
       <c r="C2" s="17"/>
       <c r="D2" s="19" t="str">
@@ -35055,11 +35055,11 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="n">
-        <v>46328</v>
+        <v>46352</v>
       </c>
       <c r="B3" s="22" t="n">
         <f aca="false">IF(A3="","",A3+6)</f>
-        <v>46334</v>
+        <v>46358</v>
       </c>
       <c r="C3" s="17"/>
       <c r="D3" s="19" t="str">
@@ -35094,11 +35094,11 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="n">
-        <v>46335</v>
+        <v>46359</v>
       </c>
       <c r="B4" s="22" t="n">
         <f aca="false">IF(A4="","",A4+6)</f>
-        <v>46341</v>
+        <v>46365</v>
       </c>
       <c r="C4" s="17"/>
       <c r="D4" s="19" t="str">
@@ -35133,11 +35133,11 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="n">
-        <v>46342</v>
+        <v>46366</v>
       </c>
       <c r="B5" s="22" t="n">
         <f aca="false">IF(A5="","",A5+6)</f>
-        <v>46348</v>
+        <v>46372</v>
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="19" t="str">
@@ -35172,11 +35172,11 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="n">
-        <v>46349</v>
+        <v>46373</v>
       </c>
       <c r="B6" s="22" t="n">
         <f aca="false">IF(A6="","",A6+6)</f>
-        <v>46355</v>
+        <v>46379</v>
       </c>
       <c r="C6" s="17"/>
       <c r="D6" s="19" t="str">
@@ -35211,11 +35211,11 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="n">
-        <v>46356</v>
+        <v>46380</v>
       </c>
       <c r="B7" s="22" t="n">
         <f aca="false">IF(A7="","",A7+6)</f>
-        <v>46362</v>
+        <v>46386</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="19" t="str">
@@ -35250,11 +35250,11 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="n">
-        <v>46363</v>
+        <v>46387</v>
       </c>
       <c r="B8" s="22" t="n">
         <f aca="false">IF(A8="","",A8+6)</f>
-        <v>46369</v>
+        <v>46393</v>
       </c>
       <c r="C8" s="17"/>
       <c r="D8" s="19" t="str">
@@ -35289,11 +35289,11 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="n">
-        <v>46370</v>
+        <v>46394</v>
       </c>
       <c r="B9" s="22" t="n">
         <f aca="false">IF(A9="","",A9+6)</f>
-        <v>46376</v>
+        <v>46400</v>
       </c>
       <c r="C9" s="17"/>
       <c r="D9" s="19" t="str">
@@ -35328,11 +35328,11 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="n">
-        <v>46377</v>
+        <v>46401</v>
       </c>
       <c r="B10" s="22" t="n">
         <f aca="false">IF(A10="","",A10+6)</f>
-        <v>46383</v>
+        <v>46407</v>
       </c>
       <c r="C10" s="17"/>
       <c r="D10" s="19" t="str">
@@ -35367,11 +35367,11 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="n">
-        <v>46384</v>
+        <v>46408</v>
       </c>
       <c r="B11" s="22" t="n">
         <f aca="false">IF(A11="","",A11+6)</f>
-        <v>46390</v>
+        <v>46414</v>
       </c>
       <c r="C11" s="17"/>
       <c r="D11" s="19" t="str">
@@ -35406,11 +35406,11 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="n">
-        <v>46391</v>
+        <v>46415</v>
       </c>
       <c r="B12" s="22" t="n">
         <f aca="false">IF(A12="","",A12+6)</f>
-        <v>46397</v>
+        <v>46421</v>
       </c>
       <c r="C12" s="17"/>
       <c r="D12" s="19" t="str">
@@ -35445,11 +35445,11 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="n">
-        <v>46398</v>
+        <v>46422</v>
       </c>
       <c r="B13" s="22" t="n">
         <f aca="false">IF(A13="","",A13+6)</f>
-        <v>46404</v>
+        <v>46428</v>
       </c>
       <c r="C13" s="17"/>
       <c r="D13" s="19" t="str">

--- a/yontro-sheets/Yontro Content & Uploads.xlsx
+++ b/yontro-sheets/Yontro Content & Uploads.xlsx
@@ -15,12 +15,14 @@
     <sheet name="Constants" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Page KPIs" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="Team KPIs" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Variables" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Follower Targets" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Variables" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'AB Tests'!$A$1:$U$401</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Calendar!$A$1:$K$128</definedName>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Constants!$A$1:$K$151</definedName>
+    <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">'Follower Targets'!$A$1:$K$91</definedName>
     <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'Page KPIs'!$A$1:$N$61</definedName>
     <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">'Team KPIs'!$A$1:$N$31</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Uploads!$A$1:$T$401</definedName>
@@ -316,6 +318,76 @@
     <author>Unknown Author</author>
   </authors>
   <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">November 2026 runs from 19 Nov</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Instagram is the primary focus</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Month 1: type today's count. Later months fill themselves from last month's actual (or target if no actual yet).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Start x (1 + platform growth target on the Variables tab)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Lianna types this on the last day of the month</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
     <comment ref="E2" authorId="0">
       <text>
         <r>
@@ -364,12 +436,72 @@
         </r>
       </text>
     </comment>
+    <comment ref="N2" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Starting assumption, not a user figure. Sahill sets the real target here; every Follower Targets row follows.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Starting assumption, not a user figure. Sahill sets the real target here; every Follower Targets row follows.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Starting assumption, not a user figure. Sahill sets the real target here; every Follower Targets row follows.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Starting assumption, not a user figure. Sahill sets the real target here; every Follower Targets row follows.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N6" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Starting assumption, not a user figure. Sahill sets the real target here; every Follower Targets row follows.</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="169">
   <si>
     <t xml:space="preserve">Yontro Content &amp; Uploads (our own pages)</t>
   </si>
@@ -402,6 +534,9 @@
   </si>
   <si>
     <t xml:space="preserve">Team KPIs - weekly scorecard for Azeem and Lianna.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Follower Targets - followers per page per platform per month: Instagram (primary), Facebook, TikTok, YouTube Shorts, LinkedIn. Growth targets set on the Variables tab.</t>
   </si>
   <si>
     <t xml:space="preserve">Daily routine (see SOP 4):</t>
@@ -719,6 +854,48 @@
     <t xml:space="preserve">LIANNA: weekly report sent Sunday (Y/N)</t>
   </si>
   <si>
+    <t xml:space="preserve">Month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Followers at start of month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target followers at month end</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target gain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actual followers at month end</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actual gain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% of target gain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instagram</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Facebook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TikTok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YouTube Shorts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LinkedIn</t>
+  </si>
+  <si>
     <t xml:space="preserve">Variable we test</t>
   </si>
   <si>
@@ -741,6 +918,9 @@
   </si>
   <si>
     <t xml:space="preserve">Constant status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly follower growth target</t>
   </si>
   <si>
     <t xml:space="preserve">Question hook vs bold statement</t>
@@ -834,12 +1014,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd\-mmm\-yyyy"/>
     <numFmt numFmtId="166" formatCode="hh:mm"/>
     <numFmt numFmtId="167" formatCode="#,##0"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="169" formatCode="mmm\-yyyy"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -981,7 +1162,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1078,6 +1259,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="169" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1099,7 +1284,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="9">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1147,6 +1332,28 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD9F2D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF8D7DA"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <colors>
     <indexedColors>
@@ -1184,12 +1391,12 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFD9F2D9"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFF8D7DA"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -1232,6 +1439,10 @@
 </file>
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
@@ -1415,7 +1626,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:B26"/>
+  <dimension ref="B2:B27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -1480,16 +1691,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="2"/>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="3" t="s">
-        <v>11</v>
-      </c>
+      <c r="B16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1504,31 +1715,36 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="2"/>
-    </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="2" t="s">
+      <c r="B20" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="2"/>
+    </row>
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="4" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="5" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="6" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1565,37 +1781,37 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1603,7 +1819,7 @@
         <v>46344</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" s="9" t="n">
         <v>1</v>
@@ -1612,22 +1828,22 @@
         <v>0.5</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K2" s="9"/>
     </row>
@@ -1636,7 +1852,7 @@
         <v>46345</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C3" s="12" t="n">
         <v>1</v>
@@ -1645,14 +1861,14 @@
         <v>0.5</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F3" s="12"/>
       <c r="G3" s="12"/>
       <c r="H3" s="12"/>
       <c r="I3" s="12"/>
       <c r="J3" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K3" s="12"/>
     </row>
@@ -1661,7 +1877,7 @@
         <v>46345</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C4" s="12" t="n">
         <v>2</v>
@@ -1670,14 +1886,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F4" s="12"/>
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
       <c r="J4" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K4" s="12"/>
     </row>
@@ -1686,7 +1902,7 @@
         <v>46345</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C5" s="12" t="n">
         <v>3</v>
@@ -1695,14 +1911,14 @@
         <v>0.875</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F5" s="12"/>
       <c r="G5" s="12"/>
       <c r="H5" s="12"/>
       <c r="I5" s="12"/>
       <c r="J5" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K5" s="12"/>
     </row>
@@ -1711,7 +1927,7 @@
         <v>46345</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>1</v>
@@ -1720,14 +1936,14 @@
         <v>0.5</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" s="12"/>
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
       <c r="J6" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K6" s="12"/>
     </row>
@@ -1736,7 +1952,7 @@
         <v>46345</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C7" s="12" t="n">
         <v>2</v>
@@ -1745,14 +1961,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F7" s="12"/>
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
       <c r="I7" s="12"/>
       <c r="J7" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K7" s="12"/>
     </row>
@@ -1761,7 +1977,7 @@
         <v>46345</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C8" s="12" t="n">
         <v>3</v>
@@ -1770,14 +1986,14 @@
         <v>0.875</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F8" s="12"/>
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
       <c r="J8" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K8" s="12"/>
     </row>
@@ -1786,7 +2002,7 @@
         <v>46345</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>1</v>
@@ -1795,14 +2011,14 @@
         <v>0.5</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F9" s="12"/>
       <c r="G9" s="12"/>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
       <c r="J9" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K9" s="12"/>
     </row>
@@ -1811,7 +2027,7 @@
         <v>46345</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10" s="12" t="n">
         <v>2</v>
@@ -1820,14 +2036,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10" s="12"/>
       <c r="G10" s="12"/>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
       <c r="J10" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K10" s="12"/>
     </row>
@@ -1836,7 +2052,7 @@
         <v>46345</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" s="12" t="n">
         <v>3</v>
@@ -1845,14 +2061,14 @@
         <v>0.875</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F11" s="12"/>
       <c r="G11" s="12"/>
       <c r="H11" s="12"/>
       <c r="I11" s="12"/>
       <c r="J11" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K11" s="12"/>
     </row>
@@ -1861,7 +2077,7 @@
         <v>46346</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C12" s="12" t="n">
         <v>1</v>
@@ -1870,14 +2086,14 @@
         <v>0.5</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F12" s="12"/>
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
       <c r="J12" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K12" s="12"/>
     </row>
@@ -1886,7 +2102,7 @@
         <v>46346</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C13" s="12" t="n">
         <v>2</v>
@@ -1895,14 +2111,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F13" s="12"/>
       <c r="G13" s="12"/>
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
       <c r="J13" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K13" s="12"/>
     </row>
@@ -1911,7 +2127,7 @@
         <v>46346</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C14" s="12" t="n">
         <v>3</v>
@@ -1920,14 +2136,14 @@
         <v>0.875</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F14" s="12"/>
       <c r="G14" s="12"/>
       <c r="H14" s="12"/>
       <c r="I14" s="12"/>
       <c r="J14" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K14" s="12"/>
     </row>
@@ -1936,7 +2152,7 @@
         <v>46346</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C15" s="12" t="n">
         <v>1</v>
@@ -1945,14 +2161,14 @@
         <v>0.5</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="12"/>
       <c r="H15" s="12"/>
       <c r="I15" s="12"/>
       <c r="J15" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K15" s="12"/>
     </row>
@@ -1961,7 +2177,7 @@
         <v>46346</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C16" s="12" t="n">
         <v>2</v>
@@ -1970,14 +2186,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F16" s="12"/>
       <c r="G16" s="12"/>
       <c r="H16" s="12"/>
       <c r="I16" s="12"/>
       <c r="J16" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K16" s="12"/>
     </row>
@@ -1986,7 +2202,7 @@
         <v>46346</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C17" s="12" t="n">
         <v>3</v>
@@ -1995,14 +2211,14 @@
         <v>0.875</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F17" s="12"/>
       <c r="G17" s="12"/>
       <c r="H17" s="12"/>
       <c r="I17" s="12"/>
       <c r="J17" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K17" s="12"/>
     </row>
@@ -2011,7 +2227,7 @@
         <v>46346</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C18" s="12" t="n">
         <v>1</v>
@@ -2020,14 +2236,14 @@
         <v>0.5</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F18" s="12"/>
       <c r="G18" s="12"/>
       <c r="H18" s="12"/>
       <c r="I18" s="12"/>
       <c r="J18" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K18" s="12"/>
     </row>
@@ -2036,7 +2252,7 @@
         <v>46346</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C19" s="12" t="n">
         <v>2</v>
@@ -2045,14 +2261,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F19" s="12"/>
       <c r="G19" s="12"/>
       <c r="H19" s="12"/>
       <c r="I19" s="12"/>
       <c r="J19" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K19" s="12"/>
     </row>
@@ -2061,7 +2277,7 @@
         <v>46346</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C20" s="12" t="n">
         <v>3</v>
@@ -2070,14 +2286,14 @@
         <v>0.875</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F20" s="12"/>
       <c r="G20" s="12"/>
       <c r="H20" s="12"/>
       <c r="I20" s="12"/>
       <c r="J20" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K20" s="12"/>
     </row>
@@ -2086,7 +2302,7 @@
         <v>46347</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C21" s="12" t="n">
         <v>1</v>
@@ -2095,14 +2311,14 @@
         <v>0.5</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F21" s="12"/>
       <c r="G21" s="12"/>
       <c r="H21" s="12"/>
       <c r="I21" s="12"/>
       <c r="J21" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K21" s="12"/>
     </row>
@@ -2111,7 +2327,7 @@
         <v>46347</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C22" s="12" t="n">
         <v>2</v>
@@ -2120,14 +2336,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F22" s="12"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
       <c r="I22" s="12"/>
       <c r="J22" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -2136,7 +2352,7 @@
         <v>46347</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C23" s="12" t="n">
         <v>3</v>
@@ -2145,14 +2361,14 @@
         <v>0.875</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F23" s="12"/>
       <c r="G23" s="12"/>
       <c r="H23" s="12"/>
       <c r="I23" s="12"/>
       <c r="J23" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K23" s="12"/>
     </row>
@@ -2161,7 +2377,7 @@
         <v>46347</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C24" s="12" t="n">
         <v>1</v>
@@ -2170,14 +2386,14 @@
         <v>0.5</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F24" s="12"/>
       <c r="G24" s="12"/>
       <c r="H24" s="12"/>
       <c r="I24" s="12"/>
       <c r="J24" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K24" s="12"/>
     </row>
@@ -2186,7 +2402,7 @@
         <v>46347</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C25" s="12" t="n">
         <v>2</v>
@@ -2195,14 +2411,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F25" s="12"/>
       <c r="G25" s="12"/>
       <c r="H25" s="12"/>
       <c r="I25" s="12"/>
       <c r="J25" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K25" s="12"/>
     </row>
@@ -2211,7 +2427,7 @@
         <v>46347</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C26" s="12" t="n">
         <v>3</v>
@@ -2220,14 +2436,14 @@
         <v>0.875</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F26" s="12"/>
       <c r="G26" s="12"/>
       <c r="H26" s="12"/>
       <c r="I26" s="12"/>
       <c r="J26" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K26" s="12"/>
     </row>
@@ -2236,7 +2452,7 @@
         <v>46347</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C27" s="12" t="n">
         <v>1</v>
@@ -2245,14 +2461,14 @@
         <v>0.5</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F27" s="12"/>
       <c r="G27" s="12"/>
       <c r="H27" s="12"/>
       <c r="I27" s="12"/>
       <c r="J27" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K27" s="12"/>
     </row>
@@ -2261,7 +2477,7 @@
         <v>46347</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C28" s="12" t="n">
         <v>2</v>
@@ -2270,14 +2486,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F28" s="12"/>
       <c r="G28" s="12"/>
       <c r="H28" s="12"/>
       <c r="I28" s="12"/>
       <c r="J28" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K28" s="12"/>
     </row>
@@ -2286,7 +2502,7 @@
         <v>46347</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C29" s="12" t="n">
         <v>3</v>
@@ -2295,14 +2511,14 @@
         <v>0.875</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F29" s="12"/>
       <c r="G29" s="12"/>
       <c r="H29" s="12"/>
       <c r="I29" s="12"/>
       <c r="J29" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K29" s="12"/>
     </row>
@@ -2311,7 +2527,7 @@
         <v>46348</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C30" s="12" t="n">
         <v>1</v>
@@ -2320,14 +2536,14 @@
         <v>0.5</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F30" s="12"/>
       <c r="G30" s="12"/>
       <c r="H30" s="12"/>
       <c r="I30" s="12"/>
       <c r="J30" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K30" s="12"/>
     </row>
@@ -2336,7 +2552,7 @@
         <v>46348</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C31" s="12" t="n">
         <v>2</v>
@@ -2345,14 +2561,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F31" s="12"/>
       <c r="G31" s="12"/>
       <c r="H31" s="12"/>
       <c r="I31" s="12"/>
       <c r="J31" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K31" s="12"/>
     </row>
@@ -2361,7 +2577,7 @@
         <v>46348</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C32" s="12" t="n">
         <v>3</v>
@@ -2370,14 +2586,14 @@
         <v>0.875</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F32" s="12"/>
       <c r="G32" s="12"/>
       <c r="H32" s="12"/>
       <c r="I32" s="12"/>
       <c r="J32" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K32" s="12"/>
     </row>
@@ -2386,7 +2602,7 @@
         <v>46348</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C33" s="12" t="n">
         <v>1</v>
@@ -2395,14 +2611,14 @@
         <v>0.5</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F33" s="12"/>
       <c r="G33" s="12"/>
       <c r="H33" s="12"/>
       <c r="I33" s="12"/>
       <c r="J33" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K33" s="12"/>
     </row>
@@ -2411,7 +2627,7 @@
         <v>46348</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C34" s="12" t="n">
         <v>2</v>
@@ -2420,14 +2636,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F34" s="12"/>
       <c r="G34" s="12"/>
       <c r="H34" s="12"/>
       <c r="I34" s="12"/>
       <c r="J34" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K34" s="12"/>
     </row>
@@ -2436,7 +2652,7 @@
         <v>46348</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C35" s="12" t="n">
         <v>3</v>
@@ -2445,14 +2661,14 @@
         <v>0.875</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F35" s="12"/>
       <c r="G35" s="12"/>
       <c r="H35" s="12"/>
       <c r="I35" s="12"/>
       <c r="J35" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K35" s="12"/>
     </row>
@@ -2461,7 +2677,7 @@
         <v>46348</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C36" s="12" t="n">
         <v>1</v>
@@ -2470,14 +2686,14 @@
         <v>0.5</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F36" s="12"/>
       <c r="G36" s="12"/>
       <c r="H36" s="12"/>
       <c r="I36" s="12"/>
       <c r="J36" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K36" s="12"/>
     </row>
@@ -2486,7 +2702,7 @@
         <v>46348</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C37" s="12" t="n">
         <v>2</v>
@@ -2495,14 +2711,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F37" s="12"/>
       <c r="G37" s="12"/>
       <c r="H37" s="12"/>
       <c r="I37" s="12"/>
       <c r="J37" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K37" s="12"/>
     </row>
@@ -2511,7 +2727,7 @@
         <v>46348</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C38" s="12" t="n">
         <v>3</v>
@@ -2520,14 +2736,14 @@
         <v>0.875</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F38" s="12"/>
       <c r="G38" s="12"/>
       <c r="H38" s="12"/>
       <c r="I38" s="12"/>
       <c r="J38" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K38" s="12"/>
     </row>
@@ -2536,7 +2752,7 @@
         <v>46349</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C39" s="12" t="n">
         <v>1</v>
@@ -2545,14 +2761,14 @@
         <v>0.5</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F39" s="12"/>
       <c r="G39" s="12"/>
       <c r="H39" s="12"/>
       <c r="I39" s="12"/>
       <c r="J39" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K39" s="12"/>
     </row>
@@ -2561,7 +2777,7 @@
         <v>46349</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C40" s="12" t="n">
         <v>2</v>
@@ -2570,14 +2786,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F40" s="12"/>
       <c r="G40" s="12"/>
       <c r="H40" s="12"/>
       <c r="I40" s="12"/>
       <c r="J40" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K40" s="12"/>
     </row>
@@ -2586,7 +2802,7 @@
         <v>46349</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C41" s="12" t="n">
         <v>3</v>
@@ -2595,14 +2811,14 @@
         <v>0.875</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F41" s="12"/>
       <c r="G41" s="12"/>
       <c r="H41" s="12"/>
       <c r="I41" s="12"/>
       <c r="J41" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K41" s="12"/>
     </row>
@@ -2611,7 +2827,7 @@
         <v>46349</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C42" s="12" t="n">
         <v>1</v>
@@ -2620,14 +2836,14 @@
         <v>0.5</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F42" s="12"/>
       <c r="G42" s="12"/>
       <c r="H42" s="12"/>
       <c r="I42" s="12"/>
       <c r="J42" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K42" s="12"/>
     </row>
@@ -2636,7 +2852,7 @@
         <v>46349</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C43" s="12" t="n">
         <v>2</v>
@@ -2645,14 +2861,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F43" s="12"/>
       <c r="G43" s="12"/>
       <c r="H43" s="12"/>
       <c r="I43" s="12"/>
       <c r="J43" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K43" s="12"/>
     </row>
@@ -2661,7 +2877,7 @@
         <v>46349</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C44" s="12" t="n">
         <v>3</v>
@@ -2670,14 +2886,14 @@
         <v>0.875</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F44" s="12"/>
       <c r="G44" s="12"/>
       <c r="H44" s="12"/>
       <c r="I44" s="12"/>
       <c r="J44" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K44" s="12"/>
     </row>
@@ -2686,7 +2902,7 @@
         <v>46349</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C45" s="12" t="n">
         <v>1</v>
@@ -2695,14 +2911,14 @@
         <v>0.5</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F45" s="12"/>
       <c r="G45" s="12"/>
       <c r="H45" s="12"/>
       <c r="I45" s="12"/>
       <c r="J45" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K45" s="12"/>
     </row>
@@ -2711,7 +2927,7 @@
         <v>46349</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C46" s="12" t="n">
         <v>2</v>
@@ -2720,14 +2936,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F46" s="12"/>
       <c r="G46" s="12"/>
       <c r="H46" s="12"/>
       <c r="I46" s="12"/>
       <c r="J46" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K46" s="12"/>
     </row>
@@ -2736,7 +2952,7 @@
         <v>46349</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C47" s="12" t="n">
         <v>3</v>
@@ -2745,14 +2961,14 @@
         <v>0.875</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F47" s="12"/>
       <c r="G47" s="12"/>
       <c r="H47" s="12"/>
       <c r="I47" s="12"/>
       <c r="J47" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K47" s="12"/>
     </row>
@@ -2761,7 +2977,7 @@
         <v>46350</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C48" s="12" t="n">
         <v>1</v>
@@ -2770,14 +2986,14 @@
         <v>0.5</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F48" s="12"/>
       <c r="G48" s="12"/>
       <c r="H48" s="12"/>
       <c r="I48" s="12"/>
       <c r="J48" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K48" s="12"/>
     </row>
@@ -2786,7 +3002,7 @@
         <v>46350</v>
       </c>
       <c r="B49" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C49" s="12" t="n">
         <v>2</v>
@@ -2795,14 +3011,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F49" s="12"/>
       <c r="G49" s="12"/>
       <c r="H49" s="12"/>
       <c r="I49" s="12"/>
       <c r="J49" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K49" s="12"/>
     </row>
@@ -2811,7 +3027,7 @@
         <v>46350</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C50" s="12" t="n">
         <v>3</v>
@@ -2820,14 +3036,14 @@
         <v>0.875</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F50" s="12"/>
       <c r="G50" s="12"/>
       <c r="H50" s="12"/>
       <c r="I50" s="12"/>
       <c r="J50" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K50" s="12"/>
     </row>
@@ -2836,7 +3052,7 @@
         <v>46350</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C51" s="12" t="n">
         <v>1</v>
@@ -2845,14 +3061,14 @@
         <v>0.5</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F51" s="12"/>
       <c r="G51" s="12"/>
       <c r="H51" s="12"/>
       <c r="I51" s="12"/>
       <c r="J51" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K51" s="12"/>
     </row>
@@ -2861,7 +3077,7 @@
         <v>46350</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C52" s="12" t="n">
         <v>2</v>
@@ -2870,14 +3086,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F52" s="12"/>
       <c r="G52" s="12"/>
       <c r="H52" s="12"/>
       <c r="I52" s="12"/>
       <c r="J52" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K52" s="12"/>
     </row>
@@ -2886,7 +3102,7 @@
         <v>46350</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C53" s="12" t="n">
         <v>3</v>
@@ -2895,14 +3111,14 @@
         <v>0.875</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F53" s="12"/>
       <c r="G53" s="12"/>
       <c r="H53" s="12"/>
       <c r="I53" s="12"/>
       <c r="J53" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K53" s="12"/>
     </row>
@@ -2911,7 +3127,7 @@
         <v>46350</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C54" s="12" t="n">
         <v>1</v>
@@ -2920,14 +3136,14 @@
         <v>0.5</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F54" s="12"/>
       <c r="G54" s="12"/>
       <c r="H54" s="12"/>
       <c r="I54" s="12"/>
       <c r="J54" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K54" s="12"/>
     </row>
@@ -2936,7 +3152,7 @@
         <v>46350</v>
       </c>
       <c r="B55" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C55" s="12" t="n">
         <v>2</v>
@@ -2945,14 +3161,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F55" s="12"/>
       <c r="G55" s="12"/>
       <c r="H55" s="12"/>
       <c r="I55" s="12"/>
       <c r="J55" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K55" s="12"/>
     </row>
@@ -2961,7 +3177,7 @@
         <v>46350</v>
       </c>
       <c r="B56" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C56" s="12" t="n">
         <v>3</v>
@@ -2970,14 +3186,14 @@
         <v>0.875</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F56" s="12"/>
       <c r="G56" s="12"/>
       <c r="H56" s="12"/>
       <c r="I56" s="12"/>
       <c r="J56" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K56" s="12"/>
     </row>
@@ -2986,7 +3202,7 @@
         <v>46351</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C57" s="12" t="n">
         <v>1</v>
@@ -2995,14 +3211,14 @@
         <v>0.5</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F57" s="12"/>
       <c r="G57" s="12"/>
       <c r="H57" s="12"/>
       <c r="I57" s="12"/>
       <c r="J57" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K57" s="12"/>
     </row>
@@ -3011,7 +3227,7 @@
         <v>46351</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C58" s="12" t="n">
         <v>2</v>
@@ -3020,14 +3236,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F58" s="12"/>
       <c r="G58" s="12"/>
       <c r="H58" s="12"/>
       <c r="I58" s="12"/>
       <c r="J58" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K58" s="12"/>
     </row>
@@ -3036,7 +3252,7 @@
         <v>46351</v>
       </c>
       <c r="B59" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C59" s="12" t="n">
         <v>3</v>
@@ -3045,14 +3261,14 @@
         <v>0.875</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F59" s="12"/>
       <c r="G59" s="12"/>
       <c r="H59" s="12"/>
       <c r="I59" s="12"/>
       <c r="J59" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K59" s="12"/>
     </row>
@@ -3061,7 +3277,7 @@
         <v>46351</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C60" s="12" t="n">
         <v>1</v>
@@ -3070,14 +3286,14 @@
         <v>0.5</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F60" s="12"/>
       <c r="G60" s="12"/>
       <c r="H60" s="12"/>
       <c r="I60" s="12"/>
       <c r="J60" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K60" s="12"/>
     </row>
@@ -3086,7 +3302,7 @@
         <v>46351</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C61" s="12" t="n">
         <v>2</v>
@@ -3095,14 +3311,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F61" s="12"/>
       <c r="G61" s="12"/>
       <c r="H61" s="12"/>
       <c r="I61" s="12"/>
       <c r="J61" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K61" s="12"/>
     </row>
@@ -3111,7 +3327,7 @@
         <v>46351</v>
       </c>
       <c r="B62" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C62" s="12" t="n">
         <v>3</v>
@@ -3120,14 +3336,14 @@
         <v>0.875</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F62" s="12"/>
       <c r="G62" s="12"/>
       <c r="H62" s="12"/>
       <c r="I62" s="12"/>
       <c r="J62" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K62" s="12"/>
     </row>
@@ -3136,7 +3352,7 @@
         <v>46351</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C63" s="12" t="n">
         <v>1</v>
@@ -3145,14 +3361,14 @@
         <v>0.5</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F63" s="12"/>
       <c r="G63" s="12"/>
       <c r="H63" s="12"/>
       <c r="I63" s="12"/>
       <c r="J63" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K63" s="12"/>
     </row>
@@ -3161,7 +3377,7 @@
         <v>46351</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C64" s="12" t="n">
         <v>2</v>
@@ -3170,14 +3386,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F64" s="12"/>
       <c r="G64" s="12"/>
       <c r="H64" s="12"/>
       <c r="I64" s="12"/>
       <c r="J64" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K64" s="12"/>
     </row>
@@ -3186,7 +3402,7 @@
         <v>46351</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C65" s="12" t="n">
         <v>3</v>
@@ -3195,14 +3411,14 @@
         <v>0.875</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F65" s="12"/>
       <c r="G65" s="12"/>
       <c r="H65" s="12"/>
       <c r="I65" s="12"/>
       <c r="J65" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K65" s="12"/>
     </row>
@@ -3211,7 +3427,7 @@
         <v>46352</v>
       </c>
       <c r="B66" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C66" s="12" t="n">
         <v>1</v>
@@ -3220,14 +3436,14 @@
         <v>0.5</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F66" s="12"/>
       <c r="G66" s="12"/>
       <c r="H66" s="12"/>
       <c r="I66" s="12"/>
       <c r="J66" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K66" s="12"/>
     </row>
@@ -3236,7 +3452,7 @@
         <v>46352</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C67" s="12" t="n">
         <v>2</v>
@@ -3245,14 +3461,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F67" s="12"/>
       <c r="G67" s="12"/>
       <c r="H67" s="12"/>
       <c r="I67" s="12"/>
       <c r="J67" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K67" s="12"/>
     </row>
@@ -3261,7 +3477,7 @@
         <v>46352</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C68" s="12" t="n">
         <v>3</v>
@@ -3270,14 +3486,14 @@
         <v>0.875</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F68" s="12"/>
       <c r="G68" s="12"/>
       <c r="H68" s="12"/>
       <c r="I68" s="12"/>
       <c r="J68" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K68" s="12"/>
     </row>
@@ -3286,7 +3502,7 @@
         <v>46352</v>
       </c>
       <c r="B69" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C69" s="12" t="n">
         <v>1</v>
@@ -3295,14 +3511,14 @@
         <v>0.5</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F69" s="12"/>
       <c r="G69" s="12"/>
       <c r="H69" s="12"/>
       <c r="I69" s="12"/>
       <c r="J69" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K69" s="12"/>
     </row>
@@ -3311,7 +3527,7 @@
         <v>46352</v>
       </c>
       <c r="B70" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C70" s="12" t="n">
         <v>2</v>
@@ -3320,14 +3536,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F70" s="12"/>
       <c r="G70" s="12"/>
       <c r="H70" s="12"/>
       <c r="I70" s="12"/>
       <c r="J70" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K70" s="12"/>
     </row>
@@ -3336,7 +3552,7 @@
         <v>46352</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C71" s="12" t="n">
         <v>3</v>
@@ -3345,14 +3561,14 @@
         <v>0.875</v>
       </c>
       <c r="E71" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F71" s="12"/>
       <c r="G71" s="12"/>
       <c r="H71" s="12"/>
       <c r="I71" s="12"/>
       <c r="J71" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K71" s="12"/>
     </row>
@@ -3361,7 +3577,7 @@
         <v>46352</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C72" s="12" t="n">
         <v>1</v>
@@ -3370,14 +3586,14 @@
         <v>0.5</v>
       </c>
       <c r="E72" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F72" s="12"/>
       <c r="G72" s="12"/>
       <c r="H72" s="12"/>
       <c r="I72" s="12"/>
       <c r="J72" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K72" s="12"/>
     </row>
@@ -3386,7 +3602,7 @@
         <v>46352</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C73" s="12" t="n">
         <v>2</v>
@@ -3395,14 +3611,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E73" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F73" s="12"/>
       <c r="G73" s="12"/>
       <c r="H73" s="12"/>
       <c r="I73" s="12"/>
       <c r="J73" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K73" s="12"/>
     </row>
@@ -3411,7 +3627,7 @@
         <v>46352</v>
       </c>
       <c r="B74" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C74" s="12" t="n">
         <v>3</v>
@@ -3420,14 +3636,14 @@
         <v>0.875</v>
       </c>
       <c r="E74" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F74" s="12"/>
       <c r="G74" s="12"/>
       <c r="H74" s="12"/>
       <c r="I74" s="12"/>
       <c r="J74" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K74" s="12"/>
     </row>
@@ -3436,7 +3652,7 @@
         <v>46353</v>
       </c>
       <c r="B75" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C75" s="12" t="n">
         <v>1</v>
@@ -3445,14 +3661,14 @@
         <v>0.5</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F75" s="12"/>
       <c r="G75" s="12"/>
       <c r="H75" s="12"/>
       <c r="I75" s="12"/>
       <c r="J75" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K75" s="12"/>
     </row>
@@ -3461,7 +3677,7 @@
         <v>46353</v>
       </c>
       <c r="B76" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C76" s="12" t="n">
         <v>2</v>
@@ -3470,14 +3686,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E76" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F76" s="12"/>
       <c r="G76" s="12"/>
       <c r="H76" s="12"/>
       <c r="I76" s="12"/>
       <c r="J76" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K76" s="12"/>
     </row>
@@ -3486,7 +3702,7 @@
         <v>46353</v>
       </c>
       <c r="B77" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C77" s="12" t="n">
         <v>3</v>
@@ -3495,14 +3711,14 @@
         <v>0.875</v>
       </c>
       <c r="E77" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F77" s="12"/>
       <c r="G77" s="12"/>
       <c r="H77" s="12"/>
       <c r="I77" s="12"/>
       <c r="J77" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K77" s="12"/>
     </row>
@@ -3511,7 +3727,7 @@
         <v>46353</v>
       </c>
       <c r="B78" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C78" s="12" t="n">
         <v>1</v>
@@ -3520,14 +3736,14 @@
         <v>0.5</v>
       </c>
       <c r="E78" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F78" s="12"/>
       <c r="G78" s="12"/>
       <c r="H78" s="12"/>
       <c r="I78" s="12"/>
       <c r="J78" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K78" s="12"/>
     </row>
@@ -3536,7 +3752,7 @@
         <v>46353</v>
       </c>
       <c r="B79" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C79" s="12" t="n">
         <v>2</v>
@@ -3545,14 +3761,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F79" s="12"/>
       <c r="G79" s="12"/>
       <c r="H79" s="12"/>
       <c r="I79" s="12"/>
       <c r="J79" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K79" s="12"/>
     </row>
@@ -3561,7 +3777,7 @@
         <v>46353</v>
       </c>
       <c r="B80" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C80" s="12" t="n">
         <v>3</v>
@@ -3570,14 +3786,14 @@
         <v>0.875</v>
       </c>
       <c r="E80" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F80" s="12"/>
       <c r="G80" s="12"/>
       <c r="H80" s="12"/>
       <c r="I80" s="12"/>
       <c r="J80" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K80" s="12"/>
     </row>
@@ -3586,7 +3802,7 @@
         <v>46353</v>
       </c>
       <c r="B81" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C81" s="12" t="n">
         <v>1</v>
@@ -3595,14 +3811,14 @@
         <v>0.5</v>
       </c>
       <c r="E81" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F81" s="12"/>
       <c r="G81" s="12"/>
       <c r="H81" s="12"/>
       <c r="I81" s="12"/>
       <c r="J81" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K81" s="12"/>
     </row>
@@ -3611,7 +3827,7 @@
         <v>46353</v>
       </c>
       <c r="B82" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C82" s="12" t="n">
         <v>2</v>
@@ -3620,14 +3836,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E82" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F82" s="12"/>
       <c r="G82" s="12"/>
       <c r="H82" s="12"/>
       <c r="I82" s="12"/>
       <c r="J82" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K82" s="12"/>
     </row>
@@ -3636,7 +3852,7 @@
         <v>46353</v>
       </c>
       <c r="B83" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C83" s="12" t="n">
         <v>3</v>
@@ -3645,14 +3861,14 @@
         <v>0.875</v>
       </c>
       <c r="E83" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F83" s="12"/>
       <c r="G83" s="12"/>
       <c r="H83" s="12"/>
       <c r="I83" s="12"/>
       <c r="J83" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K83" s="12"/>
     </row>
@@ -3661,7 +3877,7 @@
         <v>46354</v>
       </c>
       <c r="B84" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C84" s="12" t="n">
         <v>1</v>
@@ -3670,14 +3886,14 @@
         <v>0.5</v>
       </c>
       <c r="E84" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F84" s="12"/>
       <c r="G84" s="12"/>
       <c r="H84" s="12"/>
       <c r="I84" s="12"/>
       <c r="J84" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K84" s="12"/>
     </row>
@@ -3686,7 +3902,7 @@
         <v>46354</v>
       </c>
       <c r="B85" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C85" s="12" t="n">
         <v>2</v>
@@ -3695,14 +3911,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E85" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F85" s="12"/>
       <c r="G85" s="12"/>
       <c r="H85" s="12"/>
       <c r="I85" s="12"/>
       <c r="J85" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K85" s="12"/>
     </row>
@@ -3711,7 +3927,7 @@
         <v>46354</v>
       </c>
       <c r="B86" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C86" s="12" t="n">
         <v>3</v>
@@ -3720,14 +3936,14 @@
         <v>0.875</v>
       </c>
       <c r="E86" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F86" s="12"/>
       <c r="G86" s="12"/>
       <c r="H86" s="12"/>
       <c r="I86" s="12"/>
       <c r="J86" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K86" s="12"/>
     </row>
@@ -3736,7 +3952,7 @@
         <v>46354</v>
       </c>
       <c r="B87" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C87" s="12" t="n">
         <v>1</v>
@@ -3745,14 +3961,14 @@
         <v>0.5</v>
       </c>
       <c r="E87" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F87" s="12"/>
       <c r="G87" s="12"/>
       <c r="H87" s="12"/>
       <c r="I87" s="12"/>
       <c r="J87" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K87" s="12"/>
     </row>
@@ -3761,7 +3977,7 @@
         <v>46354</v>
       </c>
       <c r="B88" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C88" s="12" t="n">
         <v>2</v>
@@ -3770,14 +3986,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E88" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F88" s="12"/>
       <c r="G88" s="12"/>
       <c r="H88" s="12"/>
       <c r="I88" s="12"/>
       <c r="J88" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K88" s="12"/>
     </row>
@@ -3786,7 +4002,7 @@
         <v>46354</v>
       </c>
       <c r="B89" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C89" s="12" t="n">
         <v>3</v>
@@ -3795,14 +4011,14 @@
         <v>0.875</v>
       </c>
       <c r="E89" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F89" s="12"/>
       <c r="G89" s="12"/>
       <c r="H89" s="12"/>
       <c r="I89" s="12"/>
       <c r="J89" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K89" s="12"/>
     </row>
@@ -3811,7 +4027,7 @@
         <v>46354</v>
       </c>
       <c r="B90" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C90" s="12" t="n">
         <v>1</v>
@@ -3820,14 +4036,14 @@
         <v>0.5</v>
       </c>
       <c r="E90" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F90" s="12"/>
       <c r="G90" s="12"/>
       <c r="H90" s="12"/>
       <c r="I90" s="12"/>
       <c r="J90" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K90" s="12"/>
     </row>
@@ -3836,7 +4052,7 @@
         <v>46354</v>
       </c>
       <c r="B91" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C91" s="12" t="n">
         <v>2</v>
@@ -3845,14 +4061,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E91" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F91" s="12"/>
       <c r="G91" s="12"/>
       <c r="H91" s="12"/>
       <c r="I91" s="12"/>
       <c r="J91" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K91" s="12"/>
     </row>
@@ -3861,7 +4077,7 @@
         <v>46354</v>
       </c>
       <c r="B92" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C92" s="12" t="n">
         <v>3</v>
@@ -3870,14 +4086,14 @@
         <v>0.875</v>
       </c>
       <c r="E92" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F92" s="12"/>
       <c r="G92" s="12"/>
       <c r="H92" s="12"/>
       <c r="I92" s="12"/>
       <c r="J92" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K92" s="12"/>
     </row>
@@ -3886,7 +4102,7 @@
         <v>46355</v>
       </c>
       <c r="B93" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C93" s="12" t="n">
         <v>1</v>
@@ -3895,14 +4111,14 @@
         <v>0.5</v>
       </c>
       <c r="E93" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F93" s="12"/>
       <c r="G93" s="12"/>
       <c r="H93" s="12"/>
       <c r="I93" s="12"/>
       <c r="J93" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K93" s="12"/>
     </row>
@@ -3911,7 +4127,7 @@
         <v>46355</v>
       </c>
       <c r="B94" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C94" s="12" t="n">
         <v>2</v>
@@ -3920,14 +4136,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E94" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F94" s="12"/>
       <c r="G94" s="12"/>
       <c r="H94" s="12"/>
       <c r="I94" s="12"/>
       <c r="J94" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K94" s="12"/>
     </row>
@@ -3936,7 +4152,7 @@
         <v>46355</v>
       </c>
       <c r="B95" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C95" s="12" t="n">
         <v>3</v>
@@ -3945,14 +4161,14 @@
         <v>0.875</v>
       </c>
       <c r="E95" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F95" s="12"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12"/>
       <c r="I95" s="12"/>
       <c r="J95" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K95" s="12"/>
     </row>
@@ -3961,7 +4177,7 @@
         <v>46355</v>
       </c>
       <c r="B96" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C96" s="12" t="n">
         <v>1</v>
@@ -3970,14 +4186,14 @@
         <v>0.5</v>
       </c>
       <c r="E96" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F96" s="12"/>
       <c r="G96" s="12"/>
       <c r="H96" s="12"/>
       <c r="I96" s="12"/>
       <c r="J96" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K96" s="12"/>
     </row>
@@ -3986,7 +4202,7 @@
         <v>46355</v>
       </c>
       <c r="B97" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C97" s="12" t="n">
         <v>2</v>
@@ -3995,14 +4211,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E97" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F97" s="12"/>
       <c r="G97" s="12"/>
       <c r="H97" s="12"/>
       <c r="I97" s="12"/>
       <c r="J97" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K97" s="12"/>
     </row>
@@ -4011,7 +4227,7 @@
         <v>46355</v>
       </c>
       <c r="B98" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C98" s="12" t="n">
         <v>3</v>
@@ -4020,14 +4236,14 @@
         <v>0.875</v>
       </c>
       <c r="E98" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F98" s="12"/>
       <c r="G98" s="12"/>
       <c r="H98" s="12"/>
       <c r="I98" s="12"/>
       <c r="J98" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K98" s="12"/>
     </row>
@@ -4036,7 +4252,7 @@
         <v>46355</v>
       </c>
       <c r="B99" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C99" s="12" t="n">
         <v>1</v>
@@ -4045,14 +4261,14 @@
         <v>0.5</v>
       </c>
       <c r="E99" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F99" s="12"/>
       <c r="G99" s="12"/>
       <c r="H99" s="12"/>
       <c r="I99" s="12"/>
       <c r="J99" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K99" s="12"/>
     </row>
@@ -4061,7 +4277,7 @@
         <v>46355</v>
       </c>
       <c r="B100" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C100" s="12" t="n">
         <v>2</v>
@@ -4070,14 +4286,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E100" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F100" s="12"/>
       <c r="G100" s="12"/>
       <c r="H100" s="12"/>
       <c r="I100" s="12"/>
       <c r="J100" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K100" s="12"/>
     </row>
@@ -4086,7 +4302,7 @@
         <v>46355</v>
       </c>
       <c r="B101" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C101" s="12" t="n">
         <v>3</v>
@@ -4095,14 +4311,14 @@
         <v>0.875</v>
       </c>
       <c r="E101" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F101" s="12"/>
       <c r="G101" s="12"/>
       <c r="H101" s="12"/>
       <c r="I101" s="12"/>
       <c r="J101" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K101" s="12"/>
     </row>
@@ -4111,7 +4327,7 @@
         <v>46356</v>
       </c>
       <c r="B102" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C102" s="12" t="n">
         <v>1</v>
@@ -4120,14 +4336,14 @@
         <v>0.5</v>
       </c>
       <c r="E102" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F102" s="12"/>
       <c r="G102" s="12"/>
       <c r="H102" s="12"/>
       <c r="I102" s="12"/>
       <c r="J102" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K102" s="12"/>
     </row>
@@ -4136,7 +4352,7 @@
         <v>46356</v>
       </c>
       <c r="B103" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C103" s="12" t="n">
         <v>2</v>
@@ -4145,14 +4361,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E103" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F103" s="12"/>
       <c r="G103" s="12"/>
       <c r="H103" s="12"/>
       <c r="I103" s="12"/>
       <c r="J103" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K103" s="12"/>
     </row>
@@ -4161,7 +4377,7 @@
         <v>46356</v>
       </c>
       <c r="B104" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C104" s="12" t="n">
         <v>3</v>
@@ -4170,14 +4386,14 @@
         <v>0.875</v>
       </c>
       <c r="E104" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F104" s="12"/>
       <c r="G104" s="12"/>
       <c r="H104" s="12"/>
       <c r="I104" s="12"/>
       <c r="J104" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K104" s="12"/>
     </row>
@@ -4186,7 +4402,7 @@
         <v>46356</v>
       </c>
       <c r="B105" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C105" s="12" t="n">
         <v>1</v>
@@ -4195,14 +4411,14 @@
         <v>0.5</v>
       </c>
       <c r="E105" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F105" s="12"/>
       <c r="G105" s="12"/>
       <c r="H105" s="12"/>
       <c r="I105" s="12"/>
       <c r="J105" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K105" s="12"/>
     </row>
@@ -4211,7 +4427,7 @@
         <v>46356</v>
       </c>
       <c r="B106" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C106" s="12" t="n">
         <v>2</v>
@@ -4220,14 +4436,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E106" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F106" s="12"/>
       <c r="G106" s="12"/>
       <c r="H106" s="12"/>
       <c r="I106" s="12"/>
       <c r="J106" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K106" s="12"/>
     </row>
@@ -4236,7 +4452,7 @@
         <v>46356</v>
       </c>
       <c r="B107" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C107" s="12" t="n">
         <v>3</v>
@@ -4245,14 +4461,14 @@
         <v>0.875</v>
       </c>
       <c r="E107" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F107" s="12"/>
       <c r="G107" s="12"/>
       <c r="H107" s="12"/>
       <c r="I107" s="12"/>
       <c r="J107" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K107" s="12"/>
     </row>
@@ -4261,7 +4477,7 @@
         <v>46356</v>
       </c>
       <c r="B108" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C108" s="12" t="n">
         <v>1</v>
@@ -4270,14 +4486,14 @@
         <v>0.5</v>
       </c>
       <c r="E108" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F108" s="12"/>
       <c r="G108" s="12"/>
       <c r="H108" s="12"/>
       <c r="I108" s="12"/>
       <c r="J108" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K108" s="12"/>
     </row>
@@ -4286,7 +4502,7 @@
         <v>46356</v>
       </c>
       <c r="B109" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C109" s="12" t="n">
         <v>2</v>
@@ -4295,14 +4511,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E109" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F109" s="12"/>
       <c r="G109" s="12"/>
       <c r="H109" s="12"/>
       <c r="I109" s="12"/>
       <c r="J109" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K109" s="12"/>
     </row>
@@ -4311,7 +4527,7 @@
         <v>46356</v>
       </c>
       <c r="B110" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C110" s="12" t="n">
         <v>3</v>
@@ -4320,14 +4536,14 @@
         <v>0.875</v>
       </c>
       <c r="E110" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F110" s="12"/>
       <c r="G110" s="12"/>
       <c r="H110" s="12"/>
       <c r="I110" s="12"/>
       <c r="J110" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K110" s="12"/>
     </row>
@@ -4336,7 +4552,7 @@
         <v>46357</v>
       </c>
       <c r="B111" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C111" s="12" t="n">
         <v>1</v>
@@ -4345,14 +4561,14 @@
         <v>0.5</v>
       </c>
       <c r="E111" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F111" s="12"/>
       <c r="G111" s="12"/>
       <c r="H111" s="12"/>
       <c r="I111" s="12"/>
       <c r="J111" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K111" s="12"/>
     </row>
@@ -4361,7 +4577,7 @@
         <v>46357</v>
       </c>
       <c r="B112" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C112" s="12" t="n">
         <v>2</v>
@@ -4370,14 +4586,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E112" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F112" s="12"/>
       <c r="G112" s="12"/>
       <c r="H112" s="12"/>
       <c r="I112" s="12"/>
       <c r="J112" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K112" s="12"/>
     </row>
@@ -4386,7 +4602,7 @@
         <v>46357</v>
       </c>
       <c r="B113" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C113" s="12" t="n">
         <v>3</v>
@@ -4395,14 +4611,14 @@
         <v>0.875</v>
       </c>
       <c r="E113" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F113" s="12"/>
       <c r="G113" s="12"/>
       <c r="H113" s="12"/>
       <c r="I113" s="12"/>
       <c r="J113" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K113" s="12"/>
     </row>
@@ -4411,7 +4627,7 @@
         <v>46357</v>
       </c>
       <c r="B114" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C114" s="12" t="n">
         <v>1</v>
@@ -4420,14 +4636,14 @@
         <v>0.5</v>
       </c>
       <c r="E114" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F114" s="12"/>
       <c r="G114" s="12"/>
       <c r="H114" s="12"/>
       <c r="I114" s="12"/>
       <c r="J114" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K114" s="12"/>
     </row>
@@ -4436,7 +4652,7 @@
         <v>46357</v>
       </c>
       <c r="B115" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C115" s="12" t="n">
         <v>2</v>
@@ -4445,14 +4661,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E115" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F115" s="12"/>
       <c r="G115" s="12"/>
       <c r="H115" s="12"/>
       <c r="I115" s="12"/>
       <c r="J115" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K115" s="12"/>
     </row>
@@ -4461,7 +4677,7 @@
         <v>46357</v>
       </c>
       <c r="B116" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C116" s="12" t="n">
         <v>3</v>
@@ -4470,14 +4686,14 @@
         <v>0.875</v>
       </c>
       <c r="E116" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F116" s="12"/>
       <c r="G116" s="12"/>
       <c r="H116" s="12"/>
       <c r="I116" s="12"/>
       <c r="J116" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K116" s="12"/>
     </row>
@@ -4486,7 +4702,7 @@
         <v>46357</v>
       </c>
       <c r="B117" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C117" s="12" t="n">
         <v>1</v>
@@ -4495,14 +4711,14 @@
         <v>0.5</v>
       </c>
       <c r="E117" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F117" s="12"/>
       <c r="G117" s="12"/>
       <c r="H117" s="12"/>
       <c r="I117" s="12"/>
       <c r="J117" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K117" s="12"/>
     </row>
@@ -4511,7 +4727,7 @@
         <v>46357</v>
       </c>
       <c r="B118" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C118" s="12" t="n">
         <v>2</v>
@@ -4520,14 +4736,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E118" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F118" s="12"/>
       <c r="G118" s="12"/>
       <c r="H118" s="12"/>
       <c r="I118" s="12"/>
       <c r="J118" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K118" s="12"/>
     </row>
@@ -4536,7 +4752,7 @@
         <v>46357</v>
       </c>
       <c r="B119" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C119" s="12" t="n">
         <v>3</v>
@@ -4545,14 +4761,14 @@
         <v>0.875</v>
       </c>
       <c r="E119" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F119" s="12"/>
       <c r="G119" s="12"/>
       <c r="H119" s="12"/>
       <c r="I119" s="12"/>
       <c r="J119" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K119" s="12"/>
     </row>
@@ -4561,7 +4777,7 @@
         <v>46358</v>
       </c>
       <c r="B120" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C120" s="12" t="n">
         <v>1</v>
@@ -4570,14 +4786,14 @@
         <v>0.5</v>
       </c>
       <c r="E120" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F120" s="12"/>
       <c r="G120" s="12"/>
       <c r="H120" s="12"/>
       <c r="I120" s="12"/>
       <c r="J120" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K120" s="12"/>
     </row>
@@ -4586,7 +4802,7 @@
         <v>46358</v>
       </c>
       <c r="B121" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C121" s="12" t="n">
         <v>2</v>
@@ -4595,14 +4811,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E121" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F121" s="12"/>
       <c r="G121" s="12"/>
       <c r="H121" s="12"/>
       <c r="I121" s="12"/>
       <c r="J121" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K121" s="12"/>
     </row>
@@ -4611,7 +4827,7 @@
         <v>46358</v>
       </c>
       <c r="B122" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C122" s="12" t="n">
         <v>3</v>
@@ -4620,14 +4836,14 @@
         <v>0.875</v>
       </c>
       <c r="E122" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F122" s="12"/>
       <c r="G122" s="12"/>
       <c r="H122" s="12"/>
       <c r="I122" s="12"/>
       <c r="J122" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K122" s="12"/>
     </row>
@@ -4636,7 +4852,7 @@
         <v>46358</v>
       </c>
       <c r="B123" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C123" s="12" t="n">
         <v>1</v>
@@ -4645,14 +4861,14 @@
         <v>0.5</v>
       </c>
       <c r="E123" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F123" s="12"/>
       <c r="G123" s="12"/>
       <c r="H123" s="12"/>
       <c r="I123" s="12"/>
       <c r="J123" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K123" s="12"/>
     </row>
@@ -4661,7 +4877,7 @@
         <v>46358</v>
       </c>
       <c r="B124" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C124" s="12" t="n">
         <v>2</v>
@@ -4670,14 +4886,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E124" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F124" s="12"/>
       <c r="G124" s="12"/>
       <c r="H124" s="12"/>
       <c r="I124" s="12"/>
       <c r="J124" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K124" s="12"/>
     </row>
@@ -4686,7 +4902,7 @@
         <v>46358</v>
       </c>
       <c r="B125" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C125" s="12" t="n">
         <v>3</v>
@@ -4695,14 +4911,14 @@
         <v>0.875</v>
       </c>
       <c r="E125" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F125" s="12"/>
       <c r="G125" s="12"/>
       <c r="H125" s="12"/>
       <c r="I125" s="12"/>
       <c r="J125" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K125" s="12"/>
     </row>
@@ -4711,7 +4927,7 @@
         <v>46358</v>
       </c>
       <c r="B126" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C126" s="12" t="n">
         <v>1</v>
@@ -4720,14 +4936,14 @@
         <v>0.5</v>
       </c>
       <c r="E126" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F126" s="12"/>
       <c r="G126" s="12"/>
       <c r="H126" s="12"/>
       <c r="I126" s="12"/>
       <c r="J126" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K126" s="12"/>
     </row>
@@ -4736,7 +4952,7 @@
         <v>46358</v>
       </c>
       <c r="B127" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C127" s="12" t="n">
         <v>2</v>
@@ -4745,14 +4961,14 @@
         <v>0.708333333333333</v>
       </c>
       <c r="E127" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F127" s="12"/>
       <c r="G127" s="12"/>
       <c r="H127" s="12"/>
       <c r="I127" s="12"/>
       <c r="J127" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K127" s="12"/>
     </row>
@@ -4761,7 +4977,7 @@
         <v>46358</v>
       </c>
       <c r="B128" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C128" s="12" t="n">
         <v>3</v>
@@ -4770,14 +4986,14 @@
         <v>0.875</v>
       </c>
       <c r="E128" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F128" s="12"/>
       <c r="G128" s="12"/>
       <c r="H128" s="12"/>
       <c r="I128" s="12"/>
       <c r="J128" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K128" s="12"/>
     </row>
@@ -4846,64 +5062,64 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="R1" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="S1" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T1" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4911,28 +5127,28 @@
         <v>46344</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" s="9" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J2" s="14" t="n">
         <v>3200</v>
@@ -4966,7 +5182,7 @@
         <v>0.0865625</v>
       </c>
       <c r="T2" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14999,90 +15215,90 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R1" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S1" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T1" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U1" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B2" s="8" t="n">
         <v>46343</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H2" s="14" t="n">
         <v>900</v>
@@ -29139,37 +29355,37 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29180,23 +29396,23 @@
         <v>46344</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G2" s="16" t="n">
         <f aca="false">IF(F2="","",IFERROR(INDEX('AB Tests'!$Q:$Q,MATCH(F2,'AB Tests'!$A:$A,0)),""))</f>
         <v>0.21875</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I2" s="8"/>
       <c r="J2" s="9"/>
@@ -31631,46 +31847,46 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31682,7 +31898,7 @@
         <v>46351</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2" s="23" t="n">
         <f aca="false">IF(A2="","",COUNTIFS(Uploads!$B:$B,$C2,Uploads!$A:$A,"&gt;="&amp;$A2,Uploads!$A:$A,"&lt;="&amp;$B2))</f>
@@ -31738,7 +31954,7 @@
         <v>46351</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D3" s="23" t="n">
         <f aca="false">IF(A3="","",COUNTIFS(Uploads!$B:$B,$C3,Uploads!$A:$A,"&gt;="&amp;$A3,Uploads!$A:$A,"&lt;="&amp;$B3))</f>
@@ -31794,7 +32010,7 @@
         <v>46351</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D4" s="23" t="n">
         <f aca="false">IF(A4="","",COUNTIFS(Uploads!$B:$B,$C4,Uploads!$A:$A,"&gt;="&amp;$A4,Uploads!$A:$A,"&lt;="&amp;$B4))</f>
@@ -31850,7 +32066,7 @@
         <v>46358</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D5" s="23" t="n">
         <f aca="false">IF(A5="","",COUNTIFS(Uploads!$B:$B,$C5,Uploads!$A:$A,"&gt;="&amp;$A5,Uploads!$A:$A,"&lt;="&amp;$B5))</f>
@@ -31906,7 +32122,7 @@
         <v>46358</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D6" s="23" t="n">
         <f aca="false">IF(A6="","",COUNTIFS(Uploads!$B:$B,$C6,Uploads!$A:$A,"&gt;="&amp;$A6,Uploads!$A:$A,"&lt;="&amp;$B6))</f>
@@ -31962,7 +32178,7 @@
         <v>46358</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D7" s="23" t="n">
         <f aca="false">IF(A7="","",COUNTIFS(Uploads!$B:$B,$C7,Uploads!$A:$A,"&gt;="&amp;$A7,Uploads!$A:$A,"&lt;="&amp;$B7))</f>
@@ -32018,7 +32234,7 @@
         <v>46365</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D8" s="23" t="n">
         <f aca="false">IF(A8="","",COUNTIFS(Uploads!$B:$B,$C8,Uploads!$A:$A,"&gt;="&amp;$A8,Uploads!$A:$A,"&lt;="&amp;$B8))</f>
@@ -32074,7 +32290,7 @@
         <v>46365</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D9" s="23" t="n">
         <f aca="false">IF(A9="","",COUNTIFS(Uploads!$B:$B,$C9,Uploads!$A:$A,"&gt;="&amp;$A9,Uploads!$A:$A,"&lt;="&amp;$B9))</f>
@@ -32130,7 +32346,7 @@
         <v>46365</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D10" s="23" t="n">
         <f aca="false">IF(A10="","",COUNTIFS(Uploads!$B:$B,$C10,Uploads!$A:$A,"&gt;="&amp;$A10,Uploads!$A:$A,"&lt;="&amp;$B10))</f>
@@ -32186,7 +32402,7 @@
         <v>46372</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D11" s="23" t="n">
         <f aca="false">IF(A11="","",COUNTIFS(Uploads!$B:$B,$C11,Uploads!$A:$A,"&gt;="&amp;$A11,Uploads!$A:$A,"&lt;="&amp;$B11))</f>
@@ -32242,7 +32458,7 @@
         <v>46372</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D12" s="23" t="n">
         <f aca="false">IF(A12="","",COUNTIFS(Uploads!$B:$B,$C12,Uploads!$A:$A,"&gt;="&amp;$A12,Uploads!$A:$A,"&lt;="&amp;$B12))</f>
@@ -32298,7 +32514,7 @@
         <v>46372</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D13" s="23" t="n">
         <f aca="false">IF(A13="","",COUNTIFS(Uploads!$B:$B,$C13,Uploads!$A:$A,"&gt;="&amp;$A13,Uploads!$A:$A,"&lt;="&amp;$B13))</f>
@@ -32354,7 +32570,7 @@
         <v>46379</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" s="23" t="n">
         <f aca="false">IF(A14="","",COUNTIFS(Uploads!$B:$B,$C14,Uploads!$A:$A,"&gt;="&amp;$A14,Uploads!$A:$A,"&lt;="&amp;$B14))</f>
@@ -32410,7 +32626,7 @@
         <v>46379</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D15" s="23" t="n">
         <f aca="false">IF(A15="","",COUNTIFS(Uploads!$B:$B,$C15,Uploads!$A:$A,"&gt;="&amp;$A15,Uploads!$A:$A,"&lt;="&amp;$B15))</f>
@@ -32466,7 +32682,7 @@
         <v>46379</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D16" s="23" t="n">
         <f aca="false">IF(A16="","",COUNTIFS(Uploads!$B:$B,$C16,Uploads!$A:$A,"&gt;="&amp;$A16,Uploads!$A:$A,"&lt;="&amp;$B16))</f>
@@ -32522,7 +32738,7 @@
         <v>46386</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D17" s="23" t="n">
         <f aca="false">IF(A17="","",COUNTIFS(Uploads!$B:$B,$C17,Uploads!$A:$A,"&gt;="&amp;$A17,Uploads!$A:$A,"&lt;="&amp;$B17))</f>
@@ -32578,7 +32794,7 @@
         <v>46386</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D18" s="23" t="n">
         <f aca="false">IF(A18="","",COUNTIFS(Uploads!$B:$B,$C18,Uploads!$A:$A,"&gt;="&amp;$A18,Uploads!$A:$A,"&lt;="&amp;$B18))</f>
@@ -32634,7 +32850,7 @@
         <v>46386</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D19" s="23" t="n">
         <f aca="false">IF(A19="","",COUNTIFS(Uploads!$B:$B,$C19,Uploads!$A:$A,"&gt;="&amp;$A19,Uploads!$A:$A,"&lt;="&amp;$B19))</f>
@@ -32690,7 +32906,7 @@
         <v>46393</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D20" s="23" t="n">
         <f aca="false">IF(A20="","",COUNTIFS(Uploads!$B:$B,$C20,Uploads!$A:$A,"&gt;="&amp;$A20,Uploads!$A:$A,"&lt;="&amp;$B20))</f>
@@ -32746,7 +32962,7 @@
         <v>46393</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D21" s="23" t="n">
         <f aca="false">IF(A21="","",COUNTIFS(Uploads!$B:$B,$C21,Uploads!$A:$A,"&gt;="&amp;$A21,Uploads!$A:$A,"&lt;="&amp;$B21))</f>
@@ -32802,7 +33018,7 @@
         <v>46393</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D22" s="23" t="n">
         <f aca="false">IF(A22="","",COUNTIFS(Uploads!$B:$B,$C22,Uploads!$A:$A,"&gt;="&amp;$A22,Uploads!$A:$A,"&lt;="&amp;$B22))</f>
@@ -32858,7 +33074,7 @@
         <v>46400</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D23" s="23" t="n">
         <f aca="false">IF(A23="","",COUNTIFS(Uploads!$B:$B,$C23,Uploads!$A:$A,"&gt;="&amp;$A23,Uploads!$A:$A,"&lt;="&amp;$B23))</f>
@@ -32914,7 +33130,7 @@
         <v>46400</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D24" s="23" t="n">
         <f aca="false">IF(A24="","",COUNTIFS(Uploads!$B:$B,$C24,Uploads!$A:$A,"&gt;="&amp;$A24,Uploads!$A:$A,"&lt;="&amp;$B24))</f>
@@ -32970,7 +33186,7 @@
         <v>46400</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D25" s="23" t="n">
         <f aca="false">IF(A25="","",COUNTIFS(Uploads!$B:$B,$C25,Uploads!$A:$A,"&gt;="&amp;$A25,Uploads!$A:$A,"&lt;="&amp;$B25))</f>
@@ -33026,7 +33242,7 @@
         <v>46407</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D26" s="23" t="n">
         <f aca="false">IF(A26="","",COUNTIFS(Uploads!$B:$B,$C26,Uploads!$A:$A,"&gt;="&amp;$A26,Uploads!$A:$A,"&lt;="&amp;$B26))</f>
@@ -33082,7 +33298,7 @@
         <v>46407</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D27" s="23" t="n">
         <f aca="false">IF(A27="","",COUNTIFS(Uploads!$B:$B,$C27,Uploads!$A:$A,"&gt;="&amp;$A27,Uploads!$A:$A,"&lt;="&amp;$B27))</f>
@@ -33138,7 +33354,7 @@
         <v>46407</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D28" s="23" t="n">
         <f aca="false">IF(A28="","",COUNTIFS(Uploads!$B:$B,$C28,Uploads!$A:$A,"&gt;="&amp;$A28,Uploads!$A:$A,"&lt;="&amp;$B28))</f>
@@ -33194,7 +33410,7 @@
         <v>46414</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D29" s="23" t="n">
         <f aca="false">IF(A29="","",COUNTIFS(Uploads!$B:$B,$C29,Uploads!$A:$A,"&gt;="&amp;$A29,Uploads!$A:$A,"&lt;="&amp;$B29))</f>
@@ -33250,7 +33466,7 @@
         <v>46414</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D30" s="23" t="n">
         <f aca="false">IF(A30="","",COUNTIFS(Uploads!$B:$B,$C30,Uploads!$A:$A,"&gt;="&amp;$A30,Uploads!$A:$A,"&lt;="&amp;$B30))</f>
@@ -33306,7 +33522,7 @@
         <v>46414</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D31" s="23" t="n">
         <f aca="false">IF(A31="","",COUNTIFS(Uploads!$B:$B,$C31,Uploads!$A:$A,"&gt;="&amp;$A31,Uploads!$A:$A,"&lt;="&amp;$B31))</f>
@@ -33362,7 +33578,7 @@
         <v>46421</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D32" s="23" t="n">
         <f aca="false">IF(A32="","",COUNTIFS(Uploads!$B:$B,$C32,Uploads!$A:$A,"&gt;="&amp;$A32,Uploads!$A:$A,"&lt;="&amp;$B32))</f>
@@ -33418,7 +33634,7 @@
         <v>46421</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D33" s="23" t="n">
         <f aca="false">IF(A33="","",COUNTIFS(Uploads!$B:$B,$C33,Uploads!$A:$A,"&gt;="&amp;$A33,Uploads!$A:$A,"&lt;="&amp;$B33))</f>
@@ -33474,7 +33690,7 @@
         <v>46421</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D34" s="23" t="n">
         <f aca="false">IF(A34="","",COUNTIFS(Uploads!$B:$B,$C34,Uploads!$A:$A,"&gt;="&amp;$A34,Uploads!$A:$A,"&lt;="&amp;$B34))</f>
@@ -33530,7 +33746,7 @@
         <v>46428</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D35" s="23" t="n">
         <f aca="false">IF(A35="","",COUNTIFS(Uploads!$B:$B,$C35,Uploads!$A:$A,"&gt;="&amp;$A35,Uploads!$A:$A,"&lt;="&amp;$B35))</f>
@@ -33586,7 +33802,7 @@
         <v>46428</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D36" s="23" t="n">
         <f aca="false">IF(A36="","",COUNTIFS(Uploads!$B:$B,$C36,Uploads!$A:$A,"&gt;="&amp;$A36,Uploads!$A:$A,"&lt;="&amp;$B36))</f>
@@ -33642,7 +33858,7 @@
         <v>46428</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D37" s="23" t="n">
         <f aca="false">IF(A37="","",COUNTIFS(Uploads!$B:$B,$C37,Uploads!$A:$A,"&gt;="&amp;$A37,Uploads!$A:$A,"&lt;="&amp;$B37))</f>
@@ -34972,46 +35188,46 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36173,7 +36389,3373 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K91"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="30"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="24" t="n">
+        <v>46327</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D2" s="21" t="str">
+        <f aca="false">IF(C2="","",IF(C2="Instagram","PRIMARY","Secondary"))</f>
+        <v>PRIMARY</v>
+      </c>
+      <c r="E2" s="17"/>
+      <c r="F2" s="23" t="str">
+        <f aca="false">IF(E2="","",ROUND(E2*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C2,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G2" s="23" t="str">
+        <f aca="false">IF(F2="","",F2-E2)</f>
+        <v/>
+      </c>
+      <c r="H2" s="17"/>
+      <c r="I2" s="23" t="str">
+        <f aca="false">IF(OR(H2="",E2=""),"",H2-E2)</f>
+        <v/>
+      </c>
+      <c r="J2" s="19" t="str">
+        <f aca="false">IF(OR(I2="",G2="",G2=0),"",I2/G2)</f>
+        <v/>
+      </c>
+      <c r="K2" s="12"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="24" t="n">
+        <v>46327</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D3" s="21" t="str">
+        <f aca="false">IF(C3="","",IF(C3="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E3" s="17"/>
+      <c r="F3" s="23" t="str">
+        <f aca="false">IF(E3="","",ROUND(E3*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C3,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G3" s="23" t="str">
+        <f aca="false">IF(F3="","",F3-E3)</f>
+        <v/>
+      </c>
+      <c r="H3" s="17"/>
+      <c r="I3" s="23" t="str">
+        <f aca="false">IF(OR(H3="",E3=""),"",H3-E3)</f>
+        <v/>
+      </c>
+      <c r="J3" s="19" t="str">
+        <f aca="false">IF(OR(I3="",G3="",G3=0),"",I3/G3)</f>
+        <v/>
+      </c>
+      <c r="K3" s="12"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="24" t="n">
+        <v>46327</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="D4" s="21" t="str">
+        <f aca="false">IF(C4="","",IF(C4="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E4" s="17"/>
+      <c r="F4" s="23" t="str">
+        <f aca="false">IF(E4="","",ROUND(E4*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C4,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G4" s="23" t="str">
+        <f aca="false">IF(F4="","",F4-E4)</f>
+        <v/>
+      </c>
+      <c r="H4" s="17"/>
+      <c r="I4" s="23" t="str">
+        <f aca="false">IF(OR(H4="",E4=""),"",H4-E4)</f>
+        <v/>
+      </c>
+      <c r="J4" s="19" t="str">
+        <f aca="false">IF(OR(I4="",G4="",G4=0),"",I4/G4)</f>
+        <v/>
+      </c>
+      <c r="K4" s="12"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="24" t="n">
+        <v>46327</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="D5" s="21" t="str">
+        <f aca="false">IF(C5="","",IF(C5="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E5" s="17"/>
+      <c r="F5" s="23" t="str">
+        <f aca="false">IF(E5="","",ROUND(E5*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C5,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G5" s="23" t="str">
+        <f aca="false">IF(F5="","",F5-E5)</f>
+        <v/>
+      </c>
+      <c r="H5" s="17"/>
+      <c r="I5" s="23" t="str">
+        <f aca="false">IF(OR(H5="",E5=""),"",H5-E5)</f>
+        <v/>
+      </c>
+      <c r="J5" s="19" t="str">
+        <f aca="false">IF(OR(I5="",G5="",G5=0),"",I5/G5)</f>
+        <v/>
+      </c>
+      <c r="K5" s="12"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="24" t="n">
+        <v>46327</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="21" t="str">
+        <f aca="false">IF(C6="","",IF(C6="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E6" s="17"/>
+      <c r="F6" s="23" t="str">
+        <f aca="false">IF(E6="","",ROUND(E6*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C6,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G6" s="23" t="str">
+        <f aca="false">IF(F6="","",F6-E6)</f>
+        <v/>
+      </c>
+      <c r="H6" s="17"/>
+      <c r="I6" s="23" t="str">
+        <f aca="false">IF(OR(H6="",E6=""),"",H6-E6)</f>
+        <v/>
+      </c>
+      <c r="J6" s="19" t="str">
+        <f aca="false">IF(OR(I6="",G6="",G6=0),"",I6/G6)</f>
+        <v/>
+      </c>
+      <c r="K6" s="12"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="24" t="n">
+        <v>46327</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D7" s="21" t="str">
+        <f aca="false">IF(C7="","",IF(C7="Instagram","PRIMARY","Secondary"))</f>
+        <v>PRIMARY</v>
+      </c>
+      <c r="E7" s="17"/>
+      <c r="F7" s="23" t="str">
+        <f aca="false">IF(E7="","",ROUND(E7*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C7,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G7" s="23" t="str">
+        <f aca="false">IF(F7="","",F7-E7)</f>
+        <v/>
+      </c>
+      <c r="H7" s="17"/>
+      <c r="I7" s="23" t="str">
+        <f aca="false">IF(OR(H7="",E7=""),"",H7-E7)</f>
+        <v/>
+      </c>
+      <c r="J7" s="19" t="str">
+        <f aca="false">IF(OR(I7="",G7="",G7=0),"",I7/G7)</f>
+        <v/>
+      </c>
+      <c r="K7" s="12"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="24" t="n">
+        <v>46327</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D8" s="21" t="str">
+        <f aca="false">IF(C8="","",IF(C8="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E8" s="17"/>
+      <c r="F8" s="23" t="str">
+        <f aca="false">IF(E8="","",ROUND(E8*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C8,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G8" s="23" t="str">
+        <f aca="false">IF(F8="","",F8-E8)</f>
+        <v/>
+      </c>
+      <c r="H8" s="17"/>
+      <c r="I8" s="23" t="str">
+        <f aca="false">IF(OR(H8="",E8=""),"",H8-E8)</f>
+        <v/>
+      </c>
+      <c r="J8" s="19" t="str">
+        <f aca="false">IF(OR(I8="",G8="",G8=0),"",I8/G8)</f>
+        <v/>
+      </c>
+      <c r="K8" s="12"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="24" t="n">
+        <v>46327</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="D9" s="21" t="str">
+        <f aca="false">IF(C9="","",IF(C9="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E9" s="17"/>
+      <c r="F9" s="23" t="str">
+        <f aca="false">IF(E9="","",ROUND(E9*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C9,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G9" s="23" t="str">
+        <f aca="false">IF(F9="","",F9-E9)</f>
+        <v/>
+      </c>
+      <c r="H9" s="17"/>
+      <c r="I9" s="23" t="str">
+        <f aca="false">IF(OR(H9="",E9=""),"",H9-E9)</f>
+        <v/>
+      </c>
+      <c r="J9" s="19" t="str">
+        <f aca="false">IF(OR(I9="",G9="",G9=0),"",I9/G9)</f>
+        <v/>
+      </c>
+      <c r="K9" s="12"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="24" t="n">
+        <v>46327</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="D10" s="21" t="str">
+        <f aca="false">IF(C10="","",IF(C10="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E10" s="17"/>
+      <c r="F10" s="23" t="str">
+        <f aca="false">IF(E10="","",ROUND(E10*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C10,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G10" s="23" t="str">
+        <f aca="false">IF(F10="","",F10-E10)</f>
+        <v/>
+      </c>
+      <c r="H10" s="17"/>
+      <c r="I10" s="23" t="str">
+        <f aca="false">IF(OR(H10="",E10=""),"",H10-E10)</f>
+        <v/>
+      </c>
+      <c r="J10" s="19" t="str">
+        <f aca="false">IF(OR(I10="",G10="",G10=0),"",I10/G10)</f>
+        <v/>
+      </c>
+      <c r="K10" s="12"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="24" t="n">
+        <v>46327</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D11" s="21" t="str">
+        <f aca="false">IF(C11="","",IF(C11="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E11" s="17"/>
+      <c r="F11" s="23" t="str">
+        <f aca="false">IF(E11="","",ROUND(E11*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C11,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G11" s="23" t="str">
+        <f aca="false">IF(F11="","",F11-E11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="17"/>
+      <c r="I11" s="23" t="str">
+        <f aca="false">IF(OR(H11="",E11=""),"",H11-E11)</f>
+        <v/>
+      </c>
+      <c r="J11" s="19" t="str">
+        <f aca="false">IF(OR(I11="",G11="",G11=0),"",I11/G11)</f>
+        <v/>
+      </c>
+      <c r="K11" s="12"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="24" t="n">
+        <v>46327</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D12" s="21" t="str">
+        <f aca="false">IF(C12="","",IF(C12="Instagram","PRIMARY","Secondary"))</f>
+        <v>PRIMARY</v>
+      </c>
+      <c r="E12" s="17"/>
+      <c r="F12" s="23" t="str">
+        <f aca="false">IF(E12="","",ROUND(E12*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C12,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G12" s="23" t="str">
+        <f aca="false">IF(F12="","",F12-E12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="17"/>
+      <c r="I12" s="23" t="str">
+        <f aca="false">IF(OR(H12="",E12=""),"",H12-E12)</f>
+        <v/>
+      </c>
+      <c r="J12" s="19" t="str">
+        <f aca="false">IF(OR(I12="",G12="",G12=0),"",I12/G12)</f>
+        <v/>
+      </c>
+      <c r="K12" s="12"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="24" t="n">
+        <v>46327</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D13" s="21" t="str">
+        <f aca="false">IF(C13="","",IF(C13="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E13" s="17"/>
+      <c r="F13" s="23" t="str">
+        <f aca="false">IF(E13="","",ROUND(E13*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C13,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G13" s="23" t="str">
+        <f aca="false">IF(F13="","",F13-E13)</f>
+        <v/>
+      </c>
+      <c r="H13" s="17"/>
+      <c r="I13" s="23" t="str">
+        <f aca="false">IF(OR(H13="",E13=""),"",H13-E13)</f>
+        <v/>
+      </c>
+      <c r="J13" s="19" t="str">
+        <f aca="false">IF(OR(I13="",G13="",G13=0),"",I13/G13)</f>
+        <v/>
+      </c>
+      <c r="K13" s="12"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="24" t="n">
+        <v>46327</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="D14" s="21" t="str">
+        <f aca="false">IF(C14="","",IF(C14="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E14" s="17"/>
+      <c r="F14" s="23" t="str">
+        <f aca="false">IF(E14="","",ROUND(E14*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C14,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G14" s="23" t="str">
+        <f aca="false">IF(F14="","",F14-E14)</f>
+        <v/>
+      </c>
+      <c r="H14" s="17"/>
+      <c r="I14" s="23" t="str">
+        <f aca="false">IF(OR(H14="",E14=""),"",H14-E14)</f>
+        <v/>
+      </c>
+      <c r="J14" s="19" t="str">
+        <f aca="false">IF(OR(I14="",G14="",G14=0),"",I14/G14)</f>
+        <v/>
+      </c>
+      <c r="K14" s="12"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="24" t="n">
+        <v>46327</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="D15" s="21" t="str">
+        <f aca="false">IF(C15="","",IF(C15="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E15" s="17"/>
+      <c r="F15" s="23" t="str">
+        <f aca="false">IF(E15="","",ROUND(E15*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C15,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G15" s="23" t="str">
+        <f aca="false">IF(F15="","",F15-E15)</f>
+        <v/>
+      </c>
+      <c r="H15" s="17"/>
+      <c r="I15" s="23" t="str">
+        <f aca="false">IF(OR(H15="",E15=""),"",H15-E15)</f>
+        <v/>
+      </c>
+      <c r="J15" s="19" t="str">
+        <f aca="false">IF(OR(I15="",G15="",G15=0),"",I15/G15)</f>
+        <v/>
+      </c>
+      <c r="K15" s="12"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="24" t="n">
+        <v>46327</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D16" s="21" t="str">
+        <f aca="false">IF(C16="","",IF(C16="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E16" s="17"/>
+      <c r="F16" s="23" t="str">
+        <f aca="false">IF(E16="","",ROUND(E16*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C16,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G16" s="23" t="str">
+        <f aca="false">IF(F16="","",F16-E16)</f>
+        <v/>
+      </c>
+      <c r="H16" s="17"/>
+      <c r="I16" s="23" t="str">
+        <f aca="false">IF(OR(H16="",E16=""),"",H16-E16)</f>
+        <v/>
+      </c>
+      <c r="J16" s="19" t="str">
+        <f aca="false">IF(OR(I16="",G16="",G16=0),"",I16/G16)</f>
+        <v/>
+      </c>
+      <c r="K16" s="12"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="24" t="n">
+        <v>46357</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D17" s="21" t="str">
+        <f aca="false">IF(C17="","",IF(C17="Instagram","PRIMARY","Secondary"))</f>
+        <v>PRIMARY</v>
+      </c>
+      <c r="E17" s="23" t="str">
+        <f aca="false">IF(H2&lt;&gt;"",H2,IF(F2="","",F2))</f>
+        <v/>
+      </c>
+      <c r="F17" s="23" t="str">
+        <f aca="false">IF(E17="","",ROUND(E17*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C17,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G17" s="23" t="str">
+        <f aca="false">IF(F17="","",F17-E17)</f>
+        <v/>
+      </c>
+      <c r="H17" s="17"/>
+      <c r="I17" s="23" t="str">
+        <f aca="false">IF(OR(H17="",E17=""),"",H17-E17)</f>
+        <v/>
+      </c>
+      <c r="J17" s="19" t="str">
+        <f aca="false">IF(OR(I17="",G17="",G17=0),"",I17/G17)</f>
+        <v/>
+      </c>
+      <c r="K17" s="12"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="24" t="n">
+        <v>46357</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D18" s="21" t="str">
+        <f aca="false">IF(C18="","",IF(C18="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E18" s="23" t="str">
+        <f aca="false">IF(H3&lt;&gt;"",H3,IF(F3="","",F3))</f>
+        <v/>
+      </c>
+      <c r="F18" s="23" t="str">
+        <f aca="false">IF(E18="","",ROUND(E18*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C18,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G18" s="23" t="str">
+        <f aca="false">IF(F18="","",F18-E18)</f>
+        <v/>
+      </c>
+      <c r="H18" s="17"/>
+      <c r="I18" s="23" t="str">
+        <f aca="false">IF(OR(H18="",E18=""),"",H18-E18)</f>
+        <v/>
+      </c>
+      <c r="J18" s="19" t="str">
+        <f aca="false">IF(OR(I18="",G18="",G18=0),"",I18/G18)</f>
+        <v/>
+      </c>
+      <c r="K18" s="12"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="24" t="n">
+        <v>46357</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="D19" s="21" t="str">
+        <f aca="false">IF(C19="","",IF(C19="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E19" s="23" t="str">
+        <f aca="false">IF(H4&lt;&gt;"",H4,IF(F4="","",F4))</f>
+        <v/>
+      </c>
+      <c r="F19" s="23" t="str">
+        <f aca="false">IF(E19="","",ROUND(E19*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C19,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G19" s="23" t="str">
+        <f aca="false">IF(F19="","",F19-E19)</f>
+        <v/>
+      </c>
+      <c r="H19" s="17"/>
+      <c r="I19" s="23" t="str">
+        <f aca="false">IF(OR(H19="",E19=""),"",H19-E19)</f>
+        <v/>
+      </c>
+      <c r="J19" s="19" t="str">
+        <f aca="false">IF(OR(I19="",G19="",G19=0),"",I19/G19)</f>
+        <v/>
+      </c>
+      <c r="K19" s="12"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="24" t="n">
+        <v>46357</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="D20" s="21" t="str">
+        <f aca="false">IF(C20="","",IF(C20="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E20" s="23" t="str">
+        <f aca="false">IF(H5&lt;&gt;"",H5,IF(F5="","",F5))</f>
+        <v/>
+      </c>
+      <c r="F20" s="23" t="str">
+        <f aca="false">IF(E20="","",ROUND(E20*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C20,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G20" s="23" t="str">
+        <f aca="false">IF(F20="","",F20-E20)</f>
+        <v/>
+      </c>
+      <c r="H20" s="17"/>
+      <c r="I20" s="23" t="str">
+        <f aca="false">IF(OR(H20="",E20=""),"",H20-E20)</f>
+        <v/>
+      </c>
+      <c r="J20" s="19" t="str">
+        <f aca="false">IF(OR(I20="",G20="",G20=0),"",I20/G20)</f>
+        <v/>
+      </c>
+      <c r="K20" s="12"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="24" t="n">
+        <v>46357</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D21" s="21" t="str">
+        <f aca="false">IF(C21="","",IF(C21="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E21" s="23" t="str">
+        <f aca="false">IF(H6&lt;&gt;"",H6,IF(F6="","",F6))</f>
+        <v/>
+      </c>
+      <c r="F21" s="23" t="str">
+        <f aca="false">IF(E21="","",ROUND(E21*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C21,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G21" s="23" t="str">
+        <f aca="false">IF(F21="","",F21-E21)</f>
+        <v/>
+      </c>
+      <c r="H21" s="17"/>
+      <c r="I21" s="23" t="str">
+        <f aca="false">IF(OR(H21="",E21=""),"",H21-E21)</f>
+        <v/>
+      </c>
+      <c r="J21" s="19" t="str">
+        <f aca="false">IF(OR(I21="",G21="",G21=0),"",I21/G21)</f>
+        <v/>
+      </c>
+      <c r="K21" s="12"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="24" t="n">
+        <v>46357</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D22" s="21" t="str">
+        <f aca="false">IF(C22="","",IF(C22="Instagram","PRIMARY","Secondary"))</f>
+        <v>PRIMARY</v>
+      </c>
+      <c r="E22" s="23" t="str">
+        <f aca="false">IF(H7&lt;&gt;"",H7,IF(F7="","",F7))</f>
+        <v/>
+      </c>
+      <c r="F22" s="23" t="str">
+        <f aca="false">IF(E22="","",ROUND(E22*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C22,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G22" s="23" t="str">
+        <f aca="false">IF(F22="","",F22-E22)</f>
+        <v/>
+      </c>
+      <c r="H22" s="17"/>
+      <c r="I22" s="23" t="str">
+        <f aca="false">IF(OR(H22="",E22=""),"",H22-E22)</f>
+        <v/>
+      </c>
+      <c r="J22" s="19" t="str">
+        <f aca="false">IF(OR(I22="",G22="",G22=0),"",I22/G22)</f>
+        <v/>
+      </c>
+      <c r="K22" s="12"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="24" t="n">
+        <v>46357</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D23" s="21" t="str">
+        <f aca="false">IF(C23="","",IF(C23="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E23" s="23" t="str">
+        <f aca="false">IF(H8&lt;&gt;"",H8,IF(F8="","",F8))</f>
+        <v/>
+      </c>
+      <c r="F23" s="23" t="str">
+        <f aca="false">IF(E23="","",ROUND(E23*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C23,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G23" s="23" t="str">
+        <f aca="false">IF(F23="","",F23-E23)</f>
+        <v/>
+      </c>
+      <c r="H23" s="17"/>
+      <c r="I23" s="23" t="str">
+        <f aca="false">IF(OR(H23="",E23=""),"",H23-E23)</f>
+        <v/>
+      </c>
+      <c r="J23" s="19" t="str">
+        <f aca="false">IF(OR(I23="",G23="",G23=0),"",I23/G23)</f>
+        <v/>
+      </c>
+      <c r="K23" s="12"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="24" t="n">
+        <v>46357</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="D24" s="21" t="str">
+        <f aca="false">IF(C24="","",IF(C24="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E24" s="23" t="str">
+        <f aca="false">IF(H9&lt;&gt;"",H9,IF(F9="","",F9))</f>
+        <v/>
+      </c>
+      <c r="F24" s="23" t="str">
+        <f aca="false">IF(E24="","",ROUND(E24*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C24,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G24" s="23" t="str">
+        <f aca="false">IF(F24="","",F24-E24)</f>
+        <v/>
+      </c>
+      <c r="H24" s="17"/>
+      <c r="I24" s="23" t="str">
+        <f aca="false">IF(OR(H24="",E24=""),"",H24-E24)</f>
+        <v/>
+      </c>
+      <c r="J24" s="19" t="str">
+        <f aca="false">IF(OR(I24="",G24="",G24=0),"",I24/G24)</f>
+        <v/>
+      </c>
+      <c r="K24" s="12"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="24" t="n">
+        <v>46357</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="D25" s="21" t="str">
+        <f aca="false">IF(C25="","",IF(C25="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E25" s="23" t="str">
+        <f aca="false">IF(H10&lt;&gt;"",H10,IF(F10="","",F10))</f>
+        <v/>
+      </c>
+      <c r="F25" s="23" t="str">
+        <f aca="false">IF(E25="","",ROUND(E25*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C25,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G25" s="23" t="str">
+        <f aca="false">IF(F25="","",F25-E25)</f>
+        <v/>
+      </c>
+      <c r="H25" s="17"/>
+      <c r="I25" s="23" t="str">
+        <f aca="false">IF(OR(H25="",E25=""),"",H25-E25)</f>
+        <v/>
+      </c>
+      <c r="J25" s="19" t="str">
+        <f aca="false">IF(OR(I25="",G25="",G25=0),"",I25/G25)</f>
+        <v/>
+      </c>
+      <c r="K25" s="12"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="24" t="n">
+        <v>46357</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D26" s="21" t="str">
+        <f aca="false">IF(C26="","",IF(C26="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E26" s="23" t="str">
+        <f aca="false">IF(H11&lt;&gt;"",H11,IF(F11="","",F11))</f>
+        <v/>
+      </c>
+      <c r="F26" s="23" t="str">
+        <f aca="false">IF(E26="","",ROUND(E26*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C26,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G26" s="23" t="str">
+        <f aca="false">IF(F26="","",F26-E26)</f>
+        <v/>
+      </c>
+      <c r="H26" s="17"/>
+      <c r="I26" s="23" t="str">
+        <f aca="false">IF(OR(H26="",E26=""),"",H26-E26)</f>
+        <v/>
+      </c>
+      <c r="J26" s="19" t="str">
+        <f aca="false">IF(OR(I26="",G26="",G26=0),"",I26/G26)</f>
+        <v/>
+      </c>
+      <c r="K26" s="12"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="24" t="n">
+        <v>46357</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D27" s="21" t="str">
+        <f aca="false">IF(C27="","",IF(C27="Instagram","PRIMARY","Secondary"))</f>
+        <v>PRIMARY</v>
+      </c>
+      <c r="E27" s="23" t="str">
+        <f aca="false">IF(H12&lt;&gt;"",H12,IF(F12="","",F12))</f>
+        <v/>
+      </c>
+      <c r="F27" s="23" t="str">
+        <f aca="false">IF(E27="","",ROUND(E27*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C27,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G27" s="23" t="str">
+        <f aca="false">IF(F27="","",F27-E27)</f>
+        <v/>
+      </c>
+      <c r="H27" s="17"/>
+      <c r="I27" s="23" t="str">
+        <f aca="false">IF(OR(H27="",E27=""),"",H27-E27)</f>
+        <v/>
+      </c>
+      <c r="J27" s="19" t="str">
+        <f aca="false">IF(OR(I27="",G27="",G27=0),"",I27/G27)</f>
+        <v/>
+      </c>
+      <c r="K27" s="12"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="24" t="n">
+        <v>46357</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D28" s="21" t="str">
+        <f aca="false">IF(C28="","",IF(C28="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E28" s="23" t="str">
+        <f aca="false">IF(H13&lt;&gt;"",H13,IF(F13="","",F13))</f>
+        <v/>
+      </c>
+      <c r="F28" s="23" t="str">
+        <f aca="false">IF(E28="","",ROUND(E28*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C28,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G28" s="23" t="str">
+        <f aca="false">IF(F28="","",F28-E28)</f>
+        <v/>
+      </c>
+      <c r="H28" s="17"/>
+      <c r="I28" s="23" t="str">
+        <f aca="false">IF(OR(H28="",E28=""),"",H28-E28)</f>
+        <v/>
+      </c>
+      <c r="J28" s="19" t="str">
+        <f aca="false">IF(OR(I28="",G28="",G28=0),"",I28/G28)</f>
+        <v/>
+      </c>
+      <c r="K28" s="12"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="24" t="n">
+        <v>46357</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="D29" s="21" t="str">
+        <f aca="false">IF(C29="","",IF(C29="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E29" s="23" t="str">
+        <f aca="false">IF(H14&lt;&gt;"",H14,IF(F14="","",F14))</f>
+        <v/>
+      </c>
+      <c r="F29" s="23" t="str">
+        <f aca="false">IF(E29="","",ROUND(E29*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C29,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G29" s="23" t="str">
+        <f aca="false">IF(F29="","",F29-E29)</f>
+        <v/>
+      </c>
+      <c r="H29" s="17"/>
+      <c r="I29" s="23" t="str">
+        <f aca="false">IF(OR(H29="",E29=""),"",H29-E29)</f>
+        <v/>
+      </c>
+      <c r="J29" s="19" t="str">
+        <f aca="false">IF(OR(I29="",G29="",G29=0),"",I29/G29)</f>
+        <v/>
+      </c>
+      <c r="K29" s="12"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="24" t="n">
+        <v>46357</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="D30" s="21" t="str">
+        <f aca="false">IF(C30="","",IF(C30="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E30" s="23" t="str">
+        <f aca="false">IF(H15&lt;&gt;"",H15,IF(F15="","",F15))</f>
+        <v/>
+      </c>
+      <c r="F30" s="23" t="str">
+        <f aca="false">IF(E30="","",ROUND(E30*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C30,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G30" s="23" t="str">
+        <f aca="false">IF(F30="","",F30-E30)</f>
+        <v/>
+      </c>
+      <c r="H30" s="17"/>
+      <c r="I30" s="23" t="str">
+        <f aca="false">IF(OR(H30="",E30=""),"",H30-E30)</f>
+        <v/>
+      </c>
+      <c r="J30" s="19" t="str">
+        <f aca="false">IF(OR(I30="",G30="",G30=0),"",I30/G30)</f>
+        <v/>
+      </c>
+      <c r="K30" s="12"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="24" t="n">
+        <v>46357</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D31" s="21" t="str">
+        <f aca="false">IF(C31="","",IF(C31="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E31" s="23" t="str">
+        <f aca="false">IF(H16&lt;&gt;"",H16,IF(F16="","",F16))</f>
+        <v/>
+      </c>
+      <c r="F31" s="23" t="str">
+        <f aca="false">IF(E31="","",ROUND(E31*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C31,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G31" s="23" t="str">
+        <f aca="false">IF(F31="","",F31-E31)</f>
+        <v/>
+      </c>
+      <c r="H31" s="17"/>
+      <c r="I31" s="23" t="str">
+        <f aca="false">IF(OR(H31="",E31=""),"",H31-E31)</f>
+        <v/>
+      </c>
+      <c r="J31" s="19" t="str">
+        <f aca="false">IF(OR(I31="",G31="",G31=0),"",I31/G31)</f>
+        <v/>
+      </c>
+      <c r="K31" s="12"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="24" t="n">
+        <v>46388</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D32" s="21" t="str">
+        <f aca="false">IF(C32="","",IF(C32="Instagram","PRIMARY","Secondary"))</f>
+        <v>PRIMARY</v>
+      </c>
+      <c r="E32" s="23" t="str">
+        <f aca="false">IF(H17&lt;&gt;"",H17,IF(F17="","",F17))</f>
+        <v/>
+      </c>
+      <c r="F32" s="23" t="str">
+        <f aca="false">IF(E32="","",ROUND(E32*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C32,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G32" s="23" t="str">
+        <f aca="false">IF(F32="","",F32-E32)</f>
+        <v/>
+      </c>
+      <c r="H32" s="17"/>
+      <c r="I32" s="23" t="str">
+        <f aca="false">IF(OR(H32="",E32=""),"",H32-E32)</f>
+        <v/>
+      </c>
+      <c r="J32" s="19" t="str">
+        <f aca="false">IF(OR(I32="",G32="",G32=0),"",I32/G32)</f>
+        <v/>
+      </c>
+      <c r="K32" s="12"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="24" t="n">
+        <v>46388</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D33" s="21" t="str">
+        <f aca="false">IF(C33="","",IF(C33="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E33" s="23" t="str">
+        <f aca="false">IF(H18&lt;&gt;"",H18,IF(F18="","",F18))</f>
+        <v/>
+      </c>
+      <c r="F33" s="23" t="str">
+        <f aca="false">IF(E33="","",ROUND(E33*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C33,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G33" s="23" t="str">
+        <f aca="false">IF(F33="","",F33-E33)</f>
+        <v/>
+      </c>
+      <c r="H33" s="17"/>
+      <c r="I33" s="23" t="str">
+        <f aca="false">IF(OR(H33="",E33=""),"",H33-E33)</f>
+        <v/>
+      </c>
+      <c r="J33" s="19" t="str">
+        <f aca="false">IF(OR(I33="",G33="",G33=0),"",I33/G33)</f>
+        <v/>
+      </c>
+      <c r="K33" s="12"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="24" t="n">
+        <v>46388</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="D34" s="21" t="str">
+        <f aca="false">IF(C34="","",IF(C34="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E34" s="23" t="str">
+        <f aca="false">IF(H19&lt;&gt;"",H19,IF(F19="","",F19))</f>
+        <v/>
+      </c>
+      <c r="F34" s="23" t="str">
+        <f aca="false">IF(E34="","",ROUND(E34*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C34,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G34" s="23" t="str">
+        <f aca="false">IF(F34="","",F34-E34)</f>
+        <v/>
+      </c>
+      <c r="H34" s="17"/>
+      <c r="I34" s="23" t="str">
+        <f aca="false">IF(OR(H34="",E34=""),"",H34-E34)</f>
+        <v/>
+      </c>
+      <c r="J34" s="19" t="str">
+        <f aca="false">IF(OR(I34="",G34="",G34=0),"",I34/G34)</f>
+        <v/>
+      </c>
+      <c r="K34" s="12"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="24" t="n">
+        <v>46388</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="D35" s="21" t="str">
+        <f aca="false">IF(C35="","",IF(C35="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E35" s="23" t="str">
+        <f aca="false">IF(H20&lt;&gt;"",H20,IF(F20="","",F20))</f>
+        <v/>
+      </c>
+      <c r="F35" s="23" t="str">
+        <f aca="false">IF(E35="","",ROUND(E35*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C35,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G35" s="23" t="str">
+        <f aca="false">IF(F35="","",F35-E35)</f>
+        <v/>
+      </c>
+      <c r="H35" s="17"/>
+      <c r="I35" s="23" t="str">
+        <f aca="false">IF(OR(H35="",E35=""),"",H35-E35)</f>
+        <v/>
+      </c>
+      <c r="J35" s="19" t="str">
+        <f aca="false">IF(OR(I35="",G35="",G35=0),"",I35/G35)</f>
+        <v/>
+      </c>
+      <c r="K35" s="12"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="24" t="n">
+        <v>46388</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D36" s="21" t="str">
+        <f aca="false">IF(C36="","",IF(C36="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E36" s="23" t="str">
+        <f aca="false">IF(H21&lt;&gt;"",H21,IF(F21="","",F21))</f>
+        <v/>
+      </c>
+      <c r="F36" s="23" t="str">
+        <f aca="false">IF(E36="","",ROUND(E36*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C36,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G36" s="23" t="str">
+        <f aca="false">IF(F36="","",F36-E36)</f>
+        <v/>
+      </c>
+      <c r="H36" s="17"/>
+      <c r="I36" s="23" t="str">
+        <f aca="false">IF(OR(H36="",E36=""),"",H36-E36)</f>
+        <v/>
+      </c>
+      <c r="J36" s="19" t="str">
+        <f aca="false">IF(OR(I36="",G36="",G36=0),"",I36/G36)</f>
+        <v/>
+      </c>
+      <c r="K36" s="12"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="24" t="n">
+        <v>46388</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D37" s="21" t="str">
+        <f aca="false">IF(C37="","",IF(C37="Instagram","PRIMARY","Secondary"))</f>
+        <v>PRIMARY</v>
+      </c>
+      <c r="E37" s="23" t="str">
+        <f aca="false">IF(H22&lt;&gt;"",H22,IF(F22="","",F22))</f>
+        <v/>
+      </c>
+      <c r="F37" s="23" t="str">
+        <f aca="false">IF(E37="","",ROUND(E37*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C37,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G37" s="23" t="str">
+        <f aca="false">IF(F37="","",F37-E37)</f>
+        <v/>
+      </c>
+      <c r="H37" s="17"/>
+      <c r="I37" s="23" t="str">
+        <f aca="false">IF(OR(H37="",E37=""),"",H37-E37)</f>
+        <v/>
+      </c>
+      <c r="J37" s="19" t="str">
+        <f aca="false">IF(OR(I37="",G37="",G37=0),"",I37/G37)</f>
+        <v/>
+      </c>
+      <c r="K37" s="12"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="24" t="n">
+        <v>46388</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D38" s="21" t="str">
+        <f aca="false">IF(C38="","",IF(C38="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E38" s="23" t="str">
+        <f aca="false">IF(H23&lt;&gt;"",H23,IF(F23="","",F23))</f>
+        <v/>
+      </c>
+      <c r="F38" s="23" t="str">
+        <f aca="false">IF(E38="","",ROUND(E38*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C38,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G38" s="23" t="str">
+        <f aca="false">IF(F38="","",F38-E38)</f>
+        <v/>
+      </c>
+      <c r="H38" s="17"/>
+      <c r="I38" s="23" t="str">
+        <f aca="false">IF(OR(H38="",E38=""),"",H38-E38)</f>
+        <v/>
+      </c>
+      <c r="J38" s="19" t="str">
+        <f aca="false">IF(OR(I38="",G38="",G38=0),"",I38/G38)</f>
+        <v/>
+      </c>
+      <c r="K38" s="12"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="24" t="n">
+        <v>46388</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="D39" s="21" t="str">
+        <f aca="false">IF(C39="","",IF(C39="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E39" s="23" t="str">
+        <f aca="false">IF(H24&lt;&gt;"",H24,IF(F24="","",F24))</f>
+        <v/>
+      </c>
+      <c r="F39" s="23" t="str">
+        <f aca="false">IF(E39="","",ROUND(E39*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C39,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G39" s="23" t="str">
+        <f aca="false">IF(F39="","",F39-E39)</f>
+        <v/>
+      </c>
+      <c r="H39" s="17"/>
+      <c r="I39" s="23" t="str">
+        <f aca="false">IF(OR(H39="",E39=""),"",H39-E39)</f>
+        <v/>
+      </c>
+      <c r="J39" s="19" t="str">
+        <f aca="false">IF(OR(I39="",G39="",G39=0),"",I39/G39)</f>
+        <v/>
+      </c>
+      <c r="K39" s="12"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="24" t="n">
+        <v>46388</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="D40" s="21" t="str">
+        <f aca="false">IF(C40="","",IF(C40="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E40" s="23" t="str">
+        <f aca="false">IF(H25&lt;&gt;"",H25,IF(F25="","",F25))</f>
+        <v/>
+      </c>
+      <c r="F40" s="23" t="str">
+        <f aca="false">IF(E40="","",ROUND(E40*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C40,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G40" s="23" t="str">
+        <f aca="false">IF(F40="","",F40-E40)</f>
+        <v/>
+      </c>
+      <c r="H40" s="17"/>
+      <c r="I40" s="23" t="str">
+        <f aca="false">IF(OR(H40="",E40=""),"",H40-E40)</f>
+        <v/>
+      </c>
+      <c r="J40" s="19" t="str">
+        <f aca="false">IF(OR(I40="",G40="",G40=0),"",I40/G40)</f>
+        <v/>
+      </c>
+      <c r="K40" s="12"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="24" t="n">
+        <v>46388</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D41" s="21" t="str">
+        <f aca="false">IF(C41="","",IF(C41="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E41" s="23" t="str">
+        <f aca="false">IF(H26&lt;&gt;"",H26,IF(F26="","",F26))</f>
+        <v/>
+      </c>
+      <c r="F41" s="23" t="str">
+        <f aca="false">IF(E41="","",ROUND(E41*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C41,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G41" s="23" t="str">
+        <f aca="false">IF(F41="","",F41-E41)</f>
+        <v/>
+      </c>
+      <c r="H41" s="17"/>
+      <c r="I41" s="23" t="str">
+        <f aca="false">IF(OR(H41="",E41=""),"",H41-E41)</f>
+        <v/>
+      </c>
+      <c r="J41" s="19" t="str">
+        <f aca="false">IF(OR(I41="",G41="",G41=0),"",I41/G41)</f>
+        <v/>
+      </c>
+      <c r="K41" s="12"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="24" t="n">
+        <v>46388</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D42" s="21" t="str">
+        <f aca="false">IF(C42="","",IF(C42="Instagram","PRIMARY","Secondary"))</f>
+        <v>PRIMARY</v>
+      </c>
+      <c r="E42" s="23" t="str">
+        <f aca="false">IF(H27&lt;&gt;"",H27,IF(F27="","",F27))</f>
+        <v/>
+      </c>
+      <c r="F42" s="23" t="str">
+        <f aca="false">IF(E42="","",ROUND(E42*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C42,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G42" s="23" t="str">
+        <f aca="false">IF(F42="","",F42-E42)</f>
+        <v/>
+      </c>
+      <c r="H42" s="17"/>
+      <c r="I42" s="23" t="str">
+        <f aca="false">IF(OR(H42="",E42=""),"",H42-E42)</f>
+        <v/>
+      </c>
+      <c r="J42" s="19" t="str">
+        <f aca="false">IF(OR(I42="",G42="",G42=0),"",I42/G42)</f>
+        <v/>
+      </c>
+      <c r="K42" s="12"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="24" t="n">
+        <v>46388</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D43" s="21" t="str">
+        <f aca="false">IF(C43="","",IF(C43="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E43" s="23" t="str">
+        <f aca="false">IF(H28&lt;&gt;"",H28,IF(F28="","",F28))</f>
+        <v/>
+      </c>
+      <c r="F43" s="23" t="str">
+        <f aca="false">IF(E43="","",ROUND(E43*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C43,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G43" s="23" t="str">
+        <f aca="false">IF(F43="","",F43-E43)</f>
+        <v/>
+      </c>
+      <c r="H43" s="17"/>
+      <c r="I43" s="23" t="str">
+        <f aca="false">IF(OR(H43="",E43=""),"",H43-E43)</f>
+        <v/>
+      </c>
+      <c r="J43" s="19" t="str">
+        <f aca="false">IF(OR(I43="",G43="",G43=0),"",I43/G43)</f>
+        <v/>
+      </c>
+      <c r="K43" s="12"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="24" t="n">
+        <v>46388</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="D44" s="21" t="str">
+        <f aca="false">IF(C44="","",IF(C44="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E44" s="23" t="str">
+        <f aca="false">IF(H29&lt;&gt;"",H29,IF(F29="","",F29))</f>
+        <v/>
+      </c>
+      <c r="F44" s="23" t="str">
+        <f aca="false">IF(E44="","",ROUND(E44*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C44,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G44" s="23" t="str">
+        <f aca="false">IF(F44="","",F44-E44)</f>
+        <v/>
+      </c>
+      <c r="H44" s="17"/>
+      <c r="I44" s="23" t="str">
+        <f aca="false">IF(OR(H44="",E44=""),"",H44-E44)</f>
+        <v/>
+      </c>
+      <c r="J44" s="19" t="str">
+        <f aca="false">IF(OR(I44="",G44="",G44=0),"",I44/G44)</f>
+        <v/>
+      </c>
+      <c r="K44" s="12"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="24" t="n">
+        <v>46388</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="D45" s="21" t="str">
+        <f aca="false">IF(C45="","",IF(C45="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E45" s="23" t="str">
+        <f aca="false">IF(H30&lt;&gt;"",H30,IF(F30="","",F30))</f>
+        <v/>
+      </c>
+      <c r="F45" s="23" t="str">
+        <f aca="false">IF(E45="","",ROUND(E45*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C45,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G45" s="23" t="str">
+        <f aca="false">IF(F45="","",F45-E45)</f>
+        <v/>
+      </c>
+      <c r="H45" s="17"/>
+      <c r="I45" s="23" t="str">
+        <f aca="false">IF(OR(H45="",E45=""),"",H45-E45)</f>
+        <v/>
+      </c>
+      <c r="J45" s="19" t="str">
+        <f aca="false">IF(OR(I45="",G45="",G45=0),"",I45/G45)</f>
+        <v/>
+      </c>
+      <c r="K45" s="12"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="24" t="n">
+        <v>46388</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D46" s="21" t="str">
+        <f aca="false">IF(C46="","",IF(C46="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E46" s="23" t="str">
+        <f aca="false">IF(H31&lt;&gt;"",H31,IF(F31="","",F31))</f>
+        <v/>
+      </c>
+      <c r="F46" s="23" t="str">
+        <f aca="false">IF(E46="","",ROUND(E46*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C46,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G46" s="23" t="str">
+        <f aca="false">IF(F46="","",F46-E46)</f>
+        <v/>
+      </c>
+      <c r="H46" s="17"/>
+      <c r="I46" s="23" t="str">
+        <f aca="false">IF(OR(H46="",E46=""),"",H46-E46)</f>
+        <v/>
+      </c>
+      <c r="J46" s="19" t="str">
+        <f aca="false">IF(OR(I46="",G46="",G46=0),"",I46/G46)</f>
+        <v/>
+      </c>
+      <c r="K46" s="12"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="24" t="n">
+        <v>46419</v>
+      </c>
+      <c r="B47" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D47" s="21" t="str">
+        <f aca="false">IF(C47="","",IF(C47="Instagram","PRIMARY","Secondary"))</f>
+        <v>PRIMARY</v>
+      </c>
+      <c r="E47" s="23" t="str">
+        <f aca="false">IF(H32&lt;&gt;"",H32,IF(F32="","",F32))</f>
+        <v/>
+      </c>
+      <c r="F47" s="23" t="str">
+        <f aca="false">IF(E47="","",ROUND(E47*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C47,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G47" s="23" t="str">
+        <f aca="false">IF(F47="","",F47-E47)</f>
+        <v/>
+      </c>
+      <c r="H47" s="17"/>
+      <c r="I47" s="23" t="str">
+        <f aca="false">IF(OR(H47="",E47=""),"",H47-E47)</f>
+        <v/>
+      </c>
+      <c r="J47" s="19" t="str">
+        <f aca="false">IF(OR(I47="",G47="",G47=0),"",I47/G47)</f>
+        <v/>
+      </c>
+      <c r="K47" s="12"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="24" t="n">
+        <v>46419</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D48" s="21" t="str">
+        <f aca="false">IF(C48="","",IF(C48="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E48" s="23" t="str">
+        <f aca="false">IF(H33&lt;&gt;"",H33,IF(F33="","",F33))</f>
+        <v/>
+      </c>
+      <c r="F48" s="23" t="str">
+        <f aca="false">IF(E48="","",ROUND(E48*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C48,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G48" s="23" t="str">
+        <f aca="false">IF(F48="","",F48-E48)</f>
+        <v/>
+      </c>
+      <c r="H48" s="17"/>
+      <c r="I48" s="23" t="str">
+        <f aca="false">IF(OR(H48="",E48=""),"",H48-E48)</f>
+        <v/>
+      </c>
+      <c r="J48" s="19" t="str">
+        <f aca="false">IF(OR(I48="",G48="",G48=0),"",I48/G48)</f>
+        <v/>
+      </c>
+      <c r="K48" s="12"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="24" t="n">
+        <v>46419</v>
+      </c>
+      <c r="B49" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="D49" s="21" t="str">
+        <f aca="false">IF(C49="","",IF(C49="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E49" s="23" t="str">
+        <f aca="false">IF(H34&lt;&gt;"",H34,IF(F34="","",F34))</f>
+        <v/>
+      </c>
+      <c r="F49" s="23" t="str">
+        <f aca="false">IF(E49="","",ROUND(E49*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C49,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G49" s="23" t="str">
+        <f aca="false">IF(F49="","",F49-E49)</f>
+        <v/>
+      </c>
+      <c r="H49" s="17"/>
+      <c r="I49" s="23" t="str">
+        <f aca="false">IF(OR(H49="",E49=""),"",H49-E49)</f>
+        <v/>
+      </c>
+      <c r="J49" s="19" t="str">
+        <f aca="false">IF(OR(I49="",G49="",G49=0),"",I49/G49)</f>
+        <v/>
+      </c>
+      <c r="K49" s="12"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="24" t="n">
+        <v>46419</v>
+      </c>
+      <c r="B50" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="D50" s="21" t="str">
+        <f aca="false">IF(C50="","",IF(C50="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E50" s="23" t="str">
+        <f aca="false">IF(H35&lt;&gt;"",H35,IF(F35="","",F35))</f>
+        <v/>
+      </c>
+      <c r="F50" s="23" t="str">
+        <f aca="false">IF(E50="","",ROUND(E50*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C50,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G50" s="23" t="str">
+        <f aca="false">IF(F50="","",F50-E50)</f>
+        <v/>
+      </c>
+      <c r="H50" s="17"/>
+      <c r="I50" s="23" t="str">
+        <f aca="false">IF(OR(H50="",E50=""),"",H50-E50)</f>
+        <v/>
+      </c>
+      <c r="J50" s="19" t="str">
+        <f aca="false">IF(OR(I50="",G50="",G50=0),"",I50/G50)</f>
+        <v/>
+      </c>
+      <c r="K50" s="12"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="24" t="n">
+        <v>46419</v>
+      </c>
+      <c r="B51" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D51" s="21" t="str">
+        <f aca="false">IF(C51="","",IF(C51="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E51" s="23" t="str">
+        <f aca="false">IF(H36&lt;&gt;"",H36,IF(F36="","",F36))</f>
+        <v/>
+      </c>
+      <c r="F51" s="23" t="str">
+        <f aca="false">IF(E51="","",ROUND(E51*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C51,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G51" s="23" t="str">
+        <f aca="false">IF(F51="","",F51-E51)</f>
+        <v/>
+      </c>
+      <c r="H51" s="17"/>
+      <c r="I51" s="23" t="str">
+        <f aca="false">IF(OR(H51="",E51=""),"",H51-E51)</f>
+        <v/>
+      </c>
+      <c r="J51" s="19" t="str">
+        <f aca="false">IF(OR(I51="",G51="",G51=0),"",I51/G51)</f>
+        <v/>
+      </c>
+      <c r="K51" s="12"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="24" t="n">
+        <v>46419</v>
+      </c>
+      <c r="B52" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D52" s="21" t="str">
+        <f aca="false">IF(C52="","",IF(C52="Instagram","PRIMARY","Secondary"))</f>
+        <v>PRIMARY</v>
+      </c>
+      <c r="E52" s="23" t="str">
+        <f aca="false">IF(H37&lt;&gt;"",H37,IF(F37="","",F37))</f>
+        <v/>
+      </c>
+      <c r="F52" s="23" t="str">
+        <f aca="false">IF(E52="","",ROUND(E52*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C52,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G52" s="23" t="str">
+        <f aca="false">IF(F52="","",F52-E52)</f>
+        <v/>
+      </c>
+      <c r="H52" s="17"/>
+      <c r="I52" s="23" t="str">
+        <f aca="false">IF(OR(H52="",E52=""),"",H52-E52)</f>
+        <v/>
+      </c>
+      <c r="J52" s="19" t="str">
+        <f aca="false">IF(OR(I52="",G52="",G52=0),"",I52/G52)</f>
+        <v/>
+      </c>
+      <c r="K52" s="12"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="24" t="n">
+        <v>46419</v>
+      </c>
+      <c r="B53" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D53" s="21" t="str">
+        <f aca="false">IF(C53="","",IF(C53="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E53" s="23" t="str">
+        <f aca="false">IF(H38&lt;&gt;"",H38,IF(F38="","",F38))</f>
+        <v/>
+      </c>
+      <c r="F53" s="23" t="str">
+        <f aca="false">IF(E53="","",ROUND(E53*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C53,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G53" s="23" t="str">
+        <f aca="false">IF(F53="","",F53-E53)</f>
+        <v/>
+      </c>
+      <c r="H53" s="17"/>
+      <c r="I53" s="23" t="str">
+        <f aca="false">IF(OR(H53="",E53=""),"",H53-E53)</f>
+        <v/>
+      </c>
+      <c r="J53" s="19" t="str">
+        <f aca="false">IF(OR(I53="",G53="",G53=0),"",I53/G53)</f>
+        <v/>
+      </c>
+      <c r="K53" s="12"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="24" t="n">
+        <v>46419</v>
+      </c>
+      <c r="B54" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="D54" s="21" t="str">
+        <f aca="false">IF(C54="","",IF(C54="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E54" s="23" t="str">
+        <f aca="false">IF(H39&lt;&gt;"",H39,IF(F39="","",F39))</f>
+        <v/>
+      </c>
+      <c r="F54" s="23" t="str">
+        <f aca="false">IF(E54="","",ROUND(E54*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C54,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G54" s="23" t="str">
+        <f aca="false">IF(F54="","",F54-E54)</f>
+        <v/>
+      </c>
+      <c r="H54" s="17"/>
+      <c r="I54" s="23" t="str">
+        <f aca="false">IF(OR(H54="",E54=""),"",H54-E54)</f>
+        <v/>
+      </c>
+      <c r="J54" s="19" t="str">
+        <f aca="false">IF(OR(I54="",G54="",G54=0),"",I54/G54)</f>
+        <v/>
+      </c>
+      <c r="K54" s="12"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="24" t="n">
+        <v>46419</v>
+      </c>
+      <c r="B55" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="D55" s="21" t="str">
+        <f aca="false">IF(C55="","",IF(C55="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E55" s="23" t="str">
+        <f aca="false">IF(H40&lt;&gt;"",H40,IF(F40="","",F40))</f>
+        <v/>
+      </c>
+      <c r="F55" s="23" t="str">
+        <f aca="false">IF(E55="","",ROUND(E55*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C55,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G55" s="23" t="str">
+        <f aca="false">IF(F55="","",F55-E55)</f>
+        <v/>
+      </c>
+      <c r="H55" s="17"/>
+      <c r="I55" s="23" t="str">
+        <f aca="false">IF(OR(H55="",E55=""),"",H55-E55)</f>
+        <v/>
+      </c>
+      <c r="J55" s="19" t="str">
+        <f aca="false">IF(OR(I55="",G55="",G55=0),"",I55/G55)</f>
+        <v/>
+      </c>
+      <c r="K55" s="12"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="24" t="n">
+        <v>46419</v>
+      </c>
+      <c r="B56" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D56" s="21" t="str">
+        <f aca="false">IF(C56="","",IF(C56="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E56" s="23" t="str">
+        <f aca="false">IF(H41&lt;&gt;"",H41,IF(F41="","",F41))</f>
+        <v/>
+      </c>
+      <c r="F56" s="23" t="str">
+        <f aca="false">IF(E56="","",ROUND(E56*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C56,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G56" s="23" t="str">
+        <f aca="false">IF(F56="","",F56-E56)</f>
+        <v/>
+      </c>
+      <c r="H56" s="17"/>
+      <c r="I56" s="23" t="str">
+        <f aca="false">IF(OR(H56="",E56=""),"",H56-E56)</f>
+        <v/>
+      </c>
+      <c r="J56" s="19" t="str">
+        <f aca="false">IF(OR(I56="",G56="",G56=0),"",I56/G56)</f>
+        <v/>
+      </c>
+      <c r="K56" s="12"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="24" t="n">
+        <v>46419</v>
+      </c>
+      <c r="B57" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D57" s="21" t="str">
+        <f aca="false">IF(C57="","",IF(C57="Instagram","PRIMARY","Secondary"))</f>
+        <v>PRIMARY</v>
+      </c>
+      <c r="E57" s="23" t="str">
+        <f aca="false">IF(H42&lt;&gt;"",H42,IF(F42="","",F42))</f>
+        <v/>
+      </c>
+      <c r="F57" s="23" t="str">
+        <f aca="false">IF(E57="","",ROUND(E57*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C57,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G57" s="23" t="str">
+        <f aca="false">IF(F57="","",F57-E57)</f>
+        <v/>
+      </c>
+      <c r="H57" s="17"/>
+      <c r="I57" s="23" t="str">
+        <f aca="false">IF(OR(H57="",E57=""),"",H57-E57)</f>
+        <v/>
+      </c>
+      <c r="J57" s="19" t="str">
+        <f aca="false">IF(OR(I57="",G57="",G57=0),"",I57/G57)</f>
+        <v/>
+      </c>
+      <c r="K57" s="12"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="24" t="n">
+        <v>46419</v>
+      </c>
+      <c r="B58" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D58" s="21" t="str">
+        <f aca="false">IF(C58="","",IF(C58="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E58" s="23" t="str">
+        <f aca="false">IF(H43&lt;&gt;"",H43,IF(F43="","",F43))</f>
+        <v/>
+      </c>
+      <c r="F58" s="23" t="str">
+        <f aca="false">IF(E58="","",ROUND(E58*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C58,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G58" s="23" t="str">
+        <f aca="false">IF(F58="","",F58-E58)</f>
+        <v/>
+      </c>
+      <c r="H58" s="17"/>
+      <c r="I58" s="23" t="str">
+        <f aca="false">IF(OR(H58="",E58=""),"",H58-E58)</f>
+        <v/>
+      </c>
+      <c r="J58" s="19" t="str">
+        <f aca="false">IF(OR(I58="",G58="",G58=0),"",I58/G58)</f>
+        <v/>
+      </c>
+      <c r="K58" s="12"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="24" t="n">
+        <v>46419</v>
+      </c>
+      <c r="B59" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="D59" s="21" t="str">
+        <f aca="false">IF(C59="","",IF(C59="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E59" s="23" t="str">
+        <f aca="false">IF(H44&lt;&gt;"",H44,IF(F44="","",F44))</f>
+        <v/>
+      </c>
+      <c r="F59" s="23" t="str">
+        <f aca="false">IF(E59="","",ROUND(E59*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C59,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G59" s="23" t="str">
+        <f aca="false">IF(F59="","",F59-E59)</f>
+        <v/>
+      </c>
+      <c r="H59" s="17"/>
+      <c r="I59" s="23" t="str">
+        <f aca="false">IF(OR(H59="",E59=""),"",H59-E59)</f>
+        <v/>
+      </c>
+      <c r="J59" s="19" t="str">
+        <f aca="false">IF(OR(I59="",G59="",G59=0),"",I59/G59)</f>
+        <v/>
+      </c>
+      <c r="K59" s="12"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="24" t="n">
+        <v>46419</v>
+      </c>
+      <c r="B60" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C60" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="D60" s="21" t="str">
+        <f aca="false">IF(C60="","",IF(C60="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E60" s="23" t="str">
+        <f aca="false">IF(H45&lt;&gt;"",H45,IF(F45="","",F45))</f>
+        <v/>
+      </c>
+      <c r="F60" s="23" t="str">
+        <f aca="false">IF(E60="","",ROUND(E60*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C60,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G60" s="23" t="str">
+        <f aca="false">IF(F60="","",F60-E60)</f>
+        <v/>
+      </c>
+      <c r="H60" s="17"/>
+      <c r="I60" s="23" t="str">
+        <f aca="false">IF(OR(H60="",E60=""),"",H60-E60)</f>
+        <v/>
+      </c>
+      <c r="J60" s="19" t="str">
+        <f aca="false">IF(OR(I60="",G60="",G60=0),"",I60/G60)</f>
+        <v/>
+      </c>
+      <c r="K60" s="12"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="24" t="n">
+        <v>46419</v>
+      </c>
+      <c r="B61" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D61" s="21" t="str">
+        <f aca="false">IF(C61="","",IF(C61="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E61" s="23" t="str">
+        <f aca="false">IF(H46&lt;&gt;"",H46,IF(F46="","",F46))</f>
+        <v/>
+      </c>
+      <c r="F61" s="23" t="str">
+        <f aca="false">IF(E61="","",ROUND(E61*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C61,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G61" s="23" t="str">
+        <f aca="false">IF(F61="","",F61-E61)</f>
+        <v/>
+      </c>
+      <c r="H61" s="17"/>
+      <c r="I61" s="23" t="str">
+        <f aca="false">IF(OR(H61="",E61=""),"",H61-E61)</f>
+        <v/>
+      </c>
+      <c r="J61" s="19" t="str">
+        <f aca="false">IF(OR(I61="",G61="",G61=0),"",I61/G61)</f>
+        <v/>
+      </c>
+      <c r="K61" s="12"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="24" t="n">
+        <v>46447</v>
+      </c>
+      <c r="B62" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D62" s="21" t="str">
+        <f aca="false">IF(C62="","",IF(C62="Instagram","PRIMARY","Secondary"))</f>
+        <v>PRIMARY</v>
+      </c>
+      <c r="E62" s="23" t="str">
+        <f aca="false">IF(H47&lt;&gt;"",H47,IF(F47="","",F47))</f>
+        <v/>
+      </c>
+      <c r="F62" s="23" t="str">
+        <f aca="false">IF(E62="","",ROUND(E62*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C62,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G62" s="23" t="str">
+        <f aca="false">IF(F62="","",F62-E62)</f>
+        <v/>
+      </c>
+      <c r="H62" s="17"/>
+      <c r="I62" s="23" t="str">
+        <f aca="false">IF(OR(H62="",E62=""),"",H62-E62)</f>
+        <v/>
+      </c>
+      <c r="J62" s="19" t="str">
+        <f aca="false">IF(OR(I62="",G62="",G62=0),"",I62/G62)</f>
+        <v/>
+      </c>
+      <c r="K62" s="12"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="24" t="n">
+        <v>46447</v>
+      </c>
+      <c r="B63" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C63" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D63" s="21" t="str">
+        <f aca="false">IF(C63="","",IF(C63="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E63" s="23" t="str">
+        <f aca="false">IF(H48&lt;&gt;"",H48,IF(F48="","",F48))</f>
+        <v/>
+      </c>
+      <c r="F63" s="23" t="str">
+        <f aca="false">IF(E63="","",ROUND(E63*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C63,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G63" s="23" t="str">
+        <f aca="false">IF(F63="","",F63-E63)</f>
+        <v/>
+      </c>
+      <c r="H63" s="17"/>
+      <c r="I63" s="23" t="str">
+        <f aca="false">IF(OR(H63="",E63=""),"",H63-E63)</f>
+        <v/>
+      </c>
+      <c r="J63" s="19" t="str">
+        <f aca="false">IF(OR(I63="",G63="",G63=0),"",I63/G63)</f>
+        <v/>
+      </c>
+      <c r="K63" s="12"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="24" t="n">
+        <v>46447</v>
+      </c>
+      <c r="B64" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C64" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="D64" s="21" t="str">
+        <f aca="false">IF(C64="","",IF(C64="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E64" s="23" t="str">
+        <f aca="false">IF(H49&lt;&gt;"",H49,IF(F49="","",F49))</f>
+        <v/>
+      </c>
+      <c r="F64" s="23" t="str">
+        <f aca="false">IF(E64="","",ROUND(E64*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C64,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G64" s="23" t="str">
+        <f aca="false">IF(F64="","",F64-E64)</f>
+        <v/>
+      </c>
+      <c r="H64" s="17"/>
+      <c r="I64" s="23" t="str">
+        <f aca="false">IF(OR(H64="",E64=""),"",H64-E64)</f>
+        <v/>
+      </c>
+      <c r="J64" s="19" t="str">
+        <f aca="false">IF(OR(I64="",G64="",G64=0),"",I64/G64)</f>
+        <v/>
+      </c>
+      <c r="K64" s="12"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="24" t="n">
+        <v>46447</v>
+      </c>
+      <c r="B65" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="D65" s="21" t="str">
+        <f aca="false">IF(C65="","",IF(C65="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E65" s="23" t="str">
+        <f aca="false">IF(H50&lt;&gt;"",H50,IF(F50="","",F50))</f>
+        <v/>
+      </c>
+      <c r="F65" s="23" t="str">
+        <f aca="false">IF(E65="","",ROUND(E65*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C65,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G65" s="23" t="str">
+        <f aca="false">IF(F65="","",F65-E65)</f>
+        <v/>
+      </c>
+      <c r="H65" s="17"/>
+      <c r="I65" s="23" t="str">
+        <f aca="false">IF(OR(H65="",E65=""),"",H65-E65)</f>
+        <v/>
+      </c>
+      <c r="J65" s="19" t="str">
+        <f aca="false">IF(OR(I65="",G65="",G65=0),"",I65/G65)</f>
+        <v/>
+      </c>
+      <c r="K65" s="12"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="24" t="n">
+        <v>46447</v>
+      </c>
+      <c r="B66" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C66" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D66" s="21" t="str">
+        <f aca="false">IF(C66="","",IF(C66="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E66" s="23" t="str">
+        <f aca="false">IF(H51&lt;&gt;"",H51,IF(F51="","",F51))</f>
+        <v/>
+      </c>
+      <c r="F66" s="23" t="str">
+        <f aca="false">IF(E66="","",ROUND(E66*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C66,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G66" s="23" t="str">
+        <f aca="false">IF(F66="","",F66-E66)</f>
+        <v/>
+      </c>
+      <c r="H66" s="17"/>
+      <c r="I66" s="23" t="str">
+        <f aca="false">IF(OR(H66="",E66=""),"",H66-E66)</f>
+        <v/>
+      </c>
+      <c r="J66" s="19" t="str">
+        <f aca="false">IF(OR(I66="",G66="",G66=0),"",I66/G66)</f>
+        <v/>
+      </c>
+      <c r="K66" s="12"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="24" t="n">
+        <v>46447</v>
+      </c>
+      <c r="B67" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D67" s="21" t="str">
+        <f aca="false">IF(C67="","",IF(C67="Instagram","PRIMARY","Secondary"))</f>
+        <v>PRIMARY</v>
+      </c>
+      <c r="E67" s="23" t="str">
+        <f aca="false">IF(H52&lt;&gt;"",H52,IF(F52="","",F52))</f>
+        <v/>
+      </c>
+      <c r="F67" s="23" t="str">
+        <f aca="false">IF(E67="","",ROUND(E67*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C67,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G67" s="23" t="str">
+        <f aca="false">IF(F67="","",F67-E67)</f>
+        <v/>
+      </c>
+      <c r="H67" s="17"/>
+      <c r="I67" s="23" t="str">
+        <f aca="false">IF(OR(H67="",E67=""),"",H67-E67)</f>
+        <v/>
+      </c>
+      <c r="J67" s="19" t="str">
+        <f aca="false">IF(OR(I67="",G67="",G67=0),"",I67/G67)</f>
+        <v/>
+      </c>
+      <c r="K67" s="12"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="24" t="n">
+        <v>46447</v>
+      </c>
+      <c r="B68" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C68" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D68" s="21" t="str">
+        <f aca="false">IF(C68="","",IF(C68="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E68" s="23" t="str">
+        <f aca="false">IF(H53&lt;&gt;"",H53,IF(F53="","",F53))</f>
+        <v/>
+      </c>
+      <c r="F68" s="23" t="str">
+        <f aca="false">IF(E68="","",ROUND(E68*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C68,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G68" s="23" t="str">
+        <f aca="false">IF(F68="","",F68-E68)</f>
+        <v/>
+      </c>
+      <c r="H68" s="17"/>
+      <c r="I68" s="23" t="str">
+        <f aca="false">IF(OR(H68="",E68=""),"",H68-E68)</f>
+        <v/>
+      </c>
+      <c r="J68" s="19" t="str">
+        <f aca="false">IF(OR(I68="",G68="",G68=0),"",I68/G68)</f>
+        <v/>
+      </c>
+      <c r="K68" s="12"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="24" t="n">
+        <v>46447</v>
+      </c>
+      <c r="B69" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C69" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="D69" s="21" t="str">
+        <f aca="false">IF(C69="","",IF(C69="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E69" s="23" t="str">
+        <f aca="false">IF(H54&lt;&gt;"",H54,IF(F54="","",F54))</f>
+        <v/>
+      </c>
+      <c r="F69" s="23" t="str">
+        <f aca="false">IF(E69="","",ROUND(E69*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C69,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G69" s="23" t="str">
+        <f aca="false">IF(F69="","",F69-E69)</f>
+        <v/>
+      </c>
+      <c r="H69" s="17"/>
+      <c r="I69" s="23" t="str">
+        <f aca="false">IF(OR(H69="",E69=""),"",H69-E69)</f>
+        <v/>
+      </c>
+      <c r="J69" s="19" t="str">
+        <f aca="false">IF(OR(I69="",G69="",G69=0),"",I69/G69)</f>
+        <v/>
+      </c>
+      <c r="K69" s="12"/>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="24" t="n">
+        <v>46447</v>
+      </c>
+      <c r="B70" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="D70" s="21" t="str">
+        <f aca="false">IF(C70="","",IF(C70="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E70" s="23" t="str">
+        <f aca="false">IF(H55&lt;&gt;"",H55,IF(F55="","",F55))</f>
+        <v/>
+      </c>
+      <c r="F70" s="23" t="str">
+        <f aca="false">IF(E70="","",ROUND(E70*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C70,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G70" s="23" t="str">
+        <f aca="false">IF(F70="","",F70-E70)</f>
+        <v/>
+      </c>
+      <c r="H70" s="17"/>
+      <c r="I70" s="23" t="str">
+        <f aca="false">IF(OR(H70="",E70=""),"",H70-E70)</f>
+        <v/>
+      </c>
+      <c r="J70" s="19" t="str">
+        <f aca="false">IF(OR(I70="",G70="",G70=0),"",I70/G70)</f>
+        <v/>
+      </c>
+      <c r="K70" s="12"/>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="24" t="n">
+        <v>46447</v>
+      </c>
+      <c r="B71" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D71" s="21" t="str">
+        <f aca="false">IF(C71="","",IF(C71="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E71" s="23" t="str">
+        <f aca="false">IF(H56&lt;&gt;"",H56,IF(F56="","",F56))</f>
+        <v/>
+      </c>
+      <c r="F71" s="23" t="str">
+        <f aca="false">IF(E71="","",ROUND(E71*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C71,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G71" s="23" t="str">
+        <f aca="false">IF(F71="","",F71-E71)</f>
+        <v/>
+      </c>
+      <c r="H71" s="17"/>
+      <c r="I71" s="23" t="str">
+        <f aca="false">IF(OR(H71="",E71=""),"",H71-E71)</f>
+        <v/>
+      </c>
+      <c r="J71" s="19" t="str">
+        <f aca="false">IF(OR(I71="",G71="",G71=0),"",I71/G71)</f>
+        <v/>
+      </c>
+      <c r="K71" s="12"/>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="24" t="n">
+        <v>46447</v>
+      </c>
+      <c r="B72" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C72" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D72" s="21" t="str">
+        <f aca="false">IF(C72="","",IF(C72="Instagram","PRIMARY","Secondary"))</f>
+        <v>PRIMARY</v>
+      </c>
+      <c r="E72" s="23" t="str">
+        <f aca="false">IF(H57&lt;&gt;"",H57,IF(F57="","",F57))</f>
+        <v/>
+      </c>
+      <c r="F72" s="23" t="str">
+        <f aca="false">IF(E72="","",ROUND(E72*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C72,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G72" s="23" t="str">
+        <f aca="false">IF(F72="","",F72-E72)</f>
+        <v/>
+      </c>
+      <c r="H72" s="17"/>
+      <c r="I72" s="23" t="str">
+        <f aca="false">IF(OR(H72="",E72=""),"",H72-E72)</f>
+        <v/>
+      </c>
+      <c r="J72" s="19" t="str">
+        <f aca="false">IF(OR(I72="",G72="",G72=0),"",I72/G72)</f>
+        <v/>
+      </c>
+      <c r="K72" s="12"/>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="24" t="n">
+        <v>46447</v>
+      </c>
+      <c r="B73" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D73" s="21" t="str">
+        <f aca="false">IF(C73="","",IF(C73="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E73" s="23" t="str">
+        <f aca="false">IF(H58&lt;&gt;"",H58,IF(F58="","",F58))</f>
+        <v/>
+      </c>
+      <c r="F73" s="23" t="str">
+        <f aca="false">IF(E73="","",ROUND(E73*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C73,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G73" s="23" t="str">
+        <f aca="false">IF(F73="","",F73-E73)</f>
+        <v/>
+      </c>
+      <c r="H73" s="17"/>
+      <c r="I73" s="23" t="str">
+        <f aca="false">IF(OR(H73="",E73=""),"",H73-E73)</f>
+        <v/>
+      </c>
+      <c r="J73" s="19" t="str">
+        <f aca="false">IF(OR(I73="",G73="",G73=0),"",I73/G73)</f>
+        <v/>
+      </c>
+      <c r="K73" s="12"/>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="24" t="n">
+        <v>46447</v>
+      </c>
+      <c r="B74" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C74" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="D74" s="21" t="str">
+        <f aca="false">IF(C74="","",IF(C74="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E74" s="23" t="str">
+        <f aca="false">IF(H59&lt;&gt;"",H59,IF(F59="","",F59))</f>
+        <v/>
+      </c>
+      <c r="F74" s="23" t="str">
+        <f aca="false">IF(E74="","",ROUND(E74*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C74,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G74" s="23" t="str">
+        <f aca="false">IF(F74="","",F74-E74)</f>
+        <v/>
+      </c>
+      <c r="H74" s="17"/>
+      <c r="I74" s="23" t="str">
+        <f aca="false">IF(OR(H74="",E74=""),"",H74-E74)</f>
+        <v/>
+      </c>
+      <c r="J74" s="19" t="str">
+        <f aca="false">IF(OR(I74="",G74="",G74=0),"",I74/G74)</f>
+        <v/>
+      </c>
+      <c r="K74" s="12"/>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="24" t="n">
+        <v>46447</v>
+      </c>
+      <c r="B75" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="D75" s="21" t="str">
+        <f aca="false">IF(C75="","",IF(C75="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E75" s="23" t="str">
+        <f aca="false">IF(H60&lt;&gt;"",H60,IF(F60="","",F60))</f>
+        <v/>
+      </c>
+      <c r="F75" s="23" t="str">
+        <f aca="false">IF(E75="","",ROUND(E75*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C75,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G75" s="23" t="str">
+        <f aca="false">IF(F75="","",F75-E75)</f>
+        <v/>
+      </c>
+      <c r="H75" s="17"/>
+      <c r="I75" s="23" t="str">
+        <f aca="false">IF(OR(H75="",E75=""),"",H75-E75)</f>
+        <v/>
+      </c>
+      <c r="J75" s="19" t="str">
+        <f aca="false">IF(OR(I75="",G75="",G75=0),"",I75/G75)</f>
+        <v/>
+      </c>
+      <c r="K75" s="12"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="24" t="n">
+        <v>46447</v>
+      </c>
+      <c r="B76" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C76" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D76" s="21" t="str">
+        <f aca="false">IF(C76="","",IF(C76="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E76" s="23" t="str">
+        <f aca="false">IF(H61&lt;&gt;"",H61,IF(F61="","",F61))</f>
+        <v/>
+      </c>
+      <c r="F76" s="23" t="str">
+        <f aca="false">IF(E76="","",ROUND(E76*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C76,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G76" s="23" t="str">
+        <f aca="false">IF(F76="","",F76-E76)</f>
+        <v/>
+      </c>
+      <c r="H76" s="17"/>
+      <c r="I76" s="23" t="str">
+        <f aca="false">IF(OR(H76="",E76=""),"",H76-E76)</f>
+        <v/>
+      </c>
+      <c r="J76" s="19" t="str">
+        <f aca="false">IF(OR(I76="",G76="",G76=0),"",I76/G76)</f>
+        <v/>
+      </c>
+      <c r="K76" s="12"/>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="24" t="n">
+        <v>46478</v>
+      </c>
+      <c r="B77" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C77" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D77" s="21" t="str">
+        <f aca="false">IF(C77="","",IF(C77="Instagram","PRIMARY","Secondary"))</f>
+        <v>PRIMARY</v>
+      </c>
+      <c r="E77" s="23" t="str">
+        <f aca="false">IF(H62&lt;&gt;"",H62,IF(F62="","",F62))</f>
+        <v/>
+      </c>
+      <c r="F77" s="23" t="str">
+        <f aca="false">IF(E77="","",ROUND(E77*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C77,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G77" s="23" t="str">
+        <f aca="false">IF(F77="","",F77-E77)</f>
+        <v/>
+      </c>
+      <c r="H77" s="17"/>
+      <c r="I77" s="23" t="str">
+        <f aca="false">IF(OR(H77="",E77=""),"",H77-E77)</f>
+        <v/>
+      </c>
+      <c r="J77" s="19" t="str">
+        <f aca="false">IF(OR(I77="",G77="",G77=0),"",I77/G77)</f>
+        <v/>
+      </c>
+      <c r="K77" s="12"/>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="24" t="n">
+        <v>46478</v>
+      </c>
+      <c r="B78" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C78" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D78" s="21" t="str">
+        <f aca="false">IF(C78="","",IF(C78="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E78" s="23" t="str">
+        <f aca="false">IF(H63&lt;&gt;"",H63,IF(F63="","",F63))</f>
+        <v/>
+      </c>
+      <c r="F78" s="23" t="str">
+        <f aca="false">IF(E78="","",ROUND(E78*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C78,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G78" s="23" t="str">
+        <f aca="false">IF(F78="","",F78-E78)</f>
+        <v/>
+      </c>
+      <c r="H78" s="17"/>
+      <c r="I78" s="23" t="str">
+        <f aca="false">IF(OR(H78="",E78=""),"",H78-E78)</f>
+        <v/>
+      </c>
+      <c r="J78" s="19" t="str">
+        <f aca="false">IF(OR(I78="",G78="",G78=0),"",I78/G78)</f>
+        <v/>
+      </c>
+      <c r="K78" s="12"/>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="24" t="n">
+        <v>46478</v>
+      </c>
+      <c r="B79" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C79" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="D79" s="21" t="str">
+        <f aca="false">IF(C79="","",IF(C79="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E79" s="23" t="str">
+        <f aca="false">IF(H64&lt;&gt;"",H64,IF(F64="","",F64))</f>
+        <v/>
+      </c>
+      <c r="F79" s="23" t="str">
+        <f aca="false">IF(E79="","",ROUND(E79*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C79,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G79" s="23" t="str">
+        <f aca="false">IF(F79="","",F79-E79)</f>
+        <v/>
+      </c>
+      <c r="H79" s="17"/>
+      <c r="I79" s="23" t="str">
+        <f aca="false">IF(OR(H79="",E79=""),"",H79-E79)</f>
+        <v/>
+      </c>
+      <c r="J79" s="19" t="str">
+        <f aca="false">IF(OR(I79="",G79="",G79=0),"",I79/G79)</f>
+        <v/>
+      </c>
+      <c r="K79" s="12"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="24" t="n">
+        <v>46478</v>
+      </c>
+      <c r="B80" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C80" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="D80" s="21" t="str">
+        <f aca="false">IF(C80="","",IF(C80="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E80" s="23" t="str">
+        <f aca="false">IF(H65&lt;&gt;"",H65,IF(F65="","",F65))</f>
+        <v/>
+      </c>
+      <c r="F80" s="23" t="str">
+        <f aca="false">IF(E80="","",ROUND(E80*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C80,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G80" s="23" t="str">
+        <f aca="false">IF(F80="","",F80-E80)</f>
+        <v/>
+      </c>
+      <c r="H80" s="17"/>
+      <c r="I80" s="23" t="str">
+        <f aca="false">IF(OR(H80="",E80=""),"",H80-E80)</f>
+        <v/>
+      </c>
+      <c r="J80" s="19" t="str">
+        <f aca="false">IF(OR(I80="",G80="",G80=0),"",I80/G80)</f>
+        <v/>
+      </c>
+      <c r="K80" s="12"/>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="24" t="n">
+        <v>46478</v>
+      </c>
+      <c r="B81" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C81" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D81" s="21" t="str">
+        <f aca="false">IF(C81="","",IF(C81="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E81" s="23" t="str">
+        <f aca="false">IF(H66&lt;&gt;"",H66,IF(F66="","",F66))</f>
+        <v/>
+      </c>
+      <c r="F81" s="23" t="str">
+        <f aca="false">IF(E81="","",ROUND(E81*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C81,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G81" s="23" t="str">
+        <f aca="false">IF(F81="","",F81-E81)</f>
+        <v/>
+      </c>
+      <c r="H81" s="17"/>
+      <c r="I81" s="23" t="str">
+        <f aca="false">IF(OR(H81="",E81=""),"",H81-E81)</f>
+        <v/>
+      </c>
+      <c r="J81" s="19" t="str">
+        <f aca="false">IF(OR(I81="",G81="",G81=0),"",I81/G81)</f>
+        <v/>
+      </c>
+      <c r="K81" s="12"/>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="24" t="n">
+        <v>46478</v>
+      </c>
+      <c r="B82" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C82" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D82" s="21" t="str">
+        <f aca="false">IF(C82="","",IF(C82="Instagram","PRIMARY","Secondary"))</f>
+        <v>PRIMARY</v>
+      </c>
+      <c r="E82" s="23" t="str">
+        <f aca="false">IF(H67&lt;&gt;"",H67,IF(F67="","",F67))</f>
+        <v/>
+      </c>
+      <c r="F82" s="23" t="str">
+        <f aca="false">IF(E82="","",ROUND(E82*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C82,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G82" s="23" t="str">
+        <f aca="false">IF(F82="","",F82-E82)</f>
+        <v/>
+      </c>
+      <c r="H82" s="17"/>
+      <c r="I82" s="23" t="str">
+        <f aca="false">IF(OR(H82="",E82=""),"",H82-E82)</f>
+        <v/>
+      </c>
+      <c r="J82" s="19" t="str">
+        <f aca="false">IF(OR(I82="",G82="",G82=0),"",I82/G82)</f>
+        <v/>
+      </c>
+      <c r="K82" s="12"/>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="24" t="n">
+        <v>46478</v>
+      </c>
+      <c r="B83" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C83" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D83" s="21" t="str">
+        <f aca="false">IF(C83="","",IF(C83="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E83" s="23" t="str">
+        <f aca="false">IF(H68&lt;&gt;"",H68,IF(F68="","",F68))</f>
+        <v/>
+      </c>
+      <c r="F83" s="23" t="str">
+        <f aca="false">IF(E83="","",ROUND(E83*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C83,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G83" s="23" t="str">
+        <f aca="false">IF(F83="","",F83-E83)</f>
+        <v/>
+      </c>
+      <c r="H83" s="17"/>
+      <c r="I83" s="23" t="str">
+        <f aca="false">IF(OR(H83="",E83=""),"",H83-E83)</f>
+        <v/>
+      </c>
+      <c r="J83" s="19" t="str">
+        <f aca="false">IF(OR(I83="",G83="",G83=0),"",I83/G83)</f>
+        <v/>
+      </c>
+      <c r="K83" s="12"/>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="24" t="n">
+        <v>46478</v>
+      </c>
+      <c r="B84" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C84" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="D84" s="21" t="str">
+        <f aca="false">IF(C84="","",IF(C84="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E84" s="23" t="str">
+        <f aca="false">IF(H69&lt;&gt;"",H69,IF(F69="","",F69))</f>
+        <v/>
+      </c>
+      <c r="F84" s="23" t="str">
+        <f aca="false">IF(E84="","",ROUND(E84*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C84,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G84" s="23" t="str">
+        <f aca="false">IF(F84="","",F84-E84)</f>
+        <v/>
+      </c>
+      <c r="H84" s="17"/>
+      <c r="I84" s="23" t="str">
+        <f aca="false">IF(OR(H84="",E84=""),"",H84-E84)</f>
+        <v/>
+      </c>
+      <c r="J84" s="19" t="str">
+        <f aca="false">IF(OR(I84="",G84="",G84=0),"",I84/G84)</f>
+        <v/>
+      </c>
+      <c r="K84" s="12"/>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="24" t="n">
+        <v>46478</v>
+      </c>
+      <c r="B85" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="D85" s="21" t="str">
+        <f aca="false">IF(C85="","",IF(C85="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E85" s="23" t="str">
+        <f aca="false">IF(H70&lt;&gt;"",H70,IF(F70="","",F70))</f>
+        <v/>
+      </c>
+      <c r="F85" s="23" t="str">
+        <f aca="false">IF(E85="","",ROUND(E85*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C85,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G85" s="23" t="str">
+        <f aca="false">IF(F85="","",F85-E85)</f>
+        <v/>
+      </c>
+      <c r="H85" s="17"/>
+      <c r="I85" s="23" t="str">
+        <f aca="false">IF(OR(H85="",E85=""),"",H85-E85)</f>
+        <v/>
+      </c>
+      <c r="J85" s="19" t="str">
+        <f aca="false">IF(OR(I85="",G85="",G85=0),"",I85/G85)</f>
+        <v/>
+      </c>
+      <c r="K85" s="12"/>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="24" t="n">
+        <v>46478</v>
+      </c>
+      <c r="B86" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C86" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D86" s="21" t="str">
+        <f aca="false">IF(C86="","",IF(C86="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E86" s="23" t="str">
+        <f aca="false">IF(H71&lt;&gt;"",H71,IF(F71="","",F71))</f>
+        <v/>
+      </c>
+      <c r="F86" s="23" t="str">
+        <f aca="false">IF(E86="","",ROUND(E86*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C86,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G86" s="23" t="str">
+        <f aca="false">IF(F86="","",F86-E86)</f>
+        <v/>
+      </c>
+      <c r="H86" s="17"/>
+      <c r="I86" s="23" t="str">
+        <f aca="false">IF(OR(H86="",E86=""),"",H86-E86)</f>
+        <v/>
+      </c>
+      <c r="J86" s="19" t="str">
+        <f aca="false">IF(OR(I86="",G86="",G86=0),"",I86/G86)</f>
+        <v/>
+      </c>
+      <c r="K86" s="12"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="24" t="n">
+        <v>46478</v>
+      </c>
+      <c r="B87" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C87" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D87" s="21" t="str">
+        <f aca="false">IF(C87="","",IF(C87="Instagram","PRIMARY","Secondary"))</f>
+        <v>PRIMARY</v>
+      </c>
+      <c r="E87" s="23" t="str">
+        <f aca="false">IF(H72&lt;&gt;"",H72,IF(F72="","",F72))</f>
+        <v/>
+      </c>
+      <c r="F87" s="23" t="str">
+        <f aca="false">IF(E87="","",ROUND(E87*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C87,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G87" s="23" t="str">
+        <f aca="false">IF(F87="","",F87-E87)</f>
+        <v/>
+      </c>
+      <c r="H87" s="17"/>
+      <c r="I87" s="23" t="str">
+        <f aca="false">IF(OR(H87="",E87=""),"",H87-E87)</f>
+        <v/>
+      </c>
+      <c r="J87" s="19" t="str">
+        <f aca="false">IF(OR(I87="",G87="",G87=0),"",I87/G87)</f>
+        <v/>
+      </c>
+      <c r="K87" s="12"/>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="24" t="n">
+        <v>46478</v>
+      </c>
+      <c r="B88" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C88" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D88" s="21" t="str">
+        <f aca="false">IF(C88="","",IF(C88="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E88" s="23" t="str">
+        <f aca="false">IF(H73&lt;&gt;"",H73,IF(F73="","",F73))</f>
+        <v/>
+      </c>
+      <c r="F88" s="23" t="str">
+        <f aca="false">IF(E88="","",ROUND(E88*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C88,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G88" s="23" t="str">
+        <f aca="false">IF(F88="","",F88-E88)</f>
+        <v/>
+      </c>
+      <c r="H88" s="17"/>
+      <c r="I88" s="23" t="str">
+        <f aca="false">IF(OR(H88="",E88=""),"",H88-E88)</f>
+        <v/>
+      </c>
+      <c r="J88" s="19" t="str">
+        <f aca="false">IF(OR(I88="",G88="",G88=0),"",I88/G88)</f>
+        <v/>
+      </c>
+      <c r="K88" s="12"/>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="24" t="n">
+        <v>46478</v>
+      </c>
+      <c r="B89" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C89" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="D89" s="21" t="str">
+        <f aca="false">IF(C89="","",IF(C89="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E89" s="23" t="str">
+        <f aca="false">IF(H74&lt;&gt;"",H74,IF(F74="","",F74))</f>
+        <v/>
+      </c>
+      <c r="F89" s="23" t="str">
+        <f aca="false">IF(E89="","",ROUND(E89*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C89,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G89" s="23" t="str">
+        <f aca="false">IF(F89="","",F89-E89)</f>
+        <v/>
+      </c>
+      <c r="H89" s="17"/>
+      <c r="I89" s="23" t="str">
+        <f aca="false">IF(OR(H89="",E89=""),"",H89-E89)</f>
+        <v/>
+      </c>
+      <c r="J89" s="19" t="str">
+        <f aca="false">IF(OR(I89="",G89="",G89=0),"",I89/G89)</f>
+        <v/>
+      </c>
+      <c r="K89" s="12"/>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="24" t="n">
+        <v>46478</v>
+      </c>
+      <c r="B90" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C90" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="D90" s="21" t="str">
+        <f aca="false">IF(C90="","",IF(C90="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E90" s="23" t="str">
+        <f aca="false">IF(H75&lt;&gt;"",H75,IF(F75="","",F75))</f>
+        <v/>
+      </c>
+      <c r="F90" s="23" t="str">
+        <f aca="false">IF(E90="","",ROUND(E90*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C90,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G90" s="23" t="str">
+        <f aca="false">IF(F90="","",F90-E90)</f>
+        <v/>
+      </c>
+      <c r="H90" s="17"/>
+      <c r="I90" s="23" t="str">
+        <f aca="false">IF(OR(H90="",E90=""),"",H90-E90)</f>
+        <v/>
+      </c>
+      <c r="J90" s="19" t="str">
+        <f aca="false">IF(OR(I90="",G90="",G90=0),"",I90/G90)</f>
+        <v/>
+      </c>
+      <c r="K90" s="12"/>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="24" t="n">
+        <v>46478</v>
+      </c>
+      <c r="B91" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C91" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D91" s="21" t="str">
+        <f aca="false">IF(C91="","",IF(C91="Instagram","PRIMARY","Secondary"))</f>
+        <v>Secondary</v>
+      </c>
+      <c r="E91" s="23" t="str">
+        <f aca="false">IF(H76&lt;&gt;"",H76,IF(F76="","",F76))</f>
+        <v/>
+      </c>
+      <c r="F91" s="23" t="str">
+        <f aca="false">IF(E91="","",ROUND(E91*(1+IFERROR(INDEX(Variables!$N$2:$N$6,MATCH(C91,Variables!$M$2:$M$6,0)),0)),0))</f>
+        <v/>
+      </c>
+      <c r="G91" s="23" t="str">
+        <f aca="false">IF(F91="","",F91-E91)</f>
+        <v/>
+      </c>
+      <c r="H91" s="17"/>
+      <c r="I91" s="23" t="str">
+        <f aca="false">IF(OR(H91="",E91=""),"",H91-E91)</f>
+        <v/>
+      </c>
+      <c r="J91" s="19" t="str">
+        <f aca="false">IF(OR(I91="",G91="",G91=0),"",I91/G91)</f>
+        <v/>
+      </c>
+      <c r="K91" s="12"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K91"/>
+  <conditionalFormatting sqref="A2:K91">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+      <formula>$C2="Instagram"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J91">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+      <formula>AND(J2&lt;&gt;"",J2&gt;=1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+      <formula>AND(J2&lt;&gt;"",J2&lt;1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -36186,184 +39768,223 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="B1" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="D1" s="24" t="s">
+      <c r="A1" s="25" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="E1" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="G1" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="H1" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="I1" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="K1" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="M1" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="E1" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="H1" s="24" t="s">
-        <v>121</v>
-      </c>
-      <c r="I1" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="J1" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="K1" s="24" t="s">
-        <v>123</v>
+      <c r="N1" s="25" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" s="25" t="s">
-        <v>124</v>
-      </c>
-      <c r="D2" s="25" t="s">
-        <v>125</v>
+      <c r="A2" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>141</v>
       </c>
       <c r="E2" s="4" t="n">
         <v>500</v>
       </c>
-      <c r="G2" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="H2" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="I2" s="25" t="s">
+      <c r="G2" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="J2" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="K2" s="25" t="s">
-        <v>94</v>
+      <c r="H2" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="J2" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="K2" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="M2" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="N2" s="27" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="25" t="s">
-        <v>126</v>
-      </c>
-      <c r="B3" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="D3" s="25" t="s">
+      <c r="A3" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="E3" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="I3" s="26" t="s">
+        <v>146</v>
+      </c>
+      <c r="J3" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="K3" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="M3" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="E3" s="26" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G3" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="H3" s="25" t="s">
-        <v>129</v>
-      </c>
-      <c r="I3" s="25" t="s">
-        <v>130</v>
-      </c>
-      <c r="J3" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="K3" s="25" t="s">
-        <v>131</v>
+      <c r="N3" s="27" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="25" t="s">
-        <v>132</v>
-      </c>
-      <c r="B4" s="25" t="s">
-        <v>133</v>
-      </c>
-      <c r="D4" s="25" t="s">
-        <v>134</v>
+      <c r="A4" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>150</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G4" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="H4" s="25" t="s">
-        <v>135</v>
-      </c>
-      <c r="I4" s="25" t="s">
-        <v>136</v>
+      <c r="G4" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="I4" s="26" t="s">
+        <v>152</v>
+      </c>
+      <c r="M4" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="N4" s="27" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="B5" s="25" t="s">
-        <v>138</v>
-      </c>
-      <c r="D5" s="25" t="s">
-        <v>139</v>
+      <c r="A5" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>155</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="I5" s="25" t="s">
-        <v>37</v>
+      <c r="I5" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="N5" s="27" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="25" t="s">
-        <v>140</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>141</v>
-      </c>
-      <c r="I6" s="25" t="s">
-        <v>142</v>
+      <c r="A6" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="I6" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="M6" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="N6" s="27" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="25" t="s">
-        <v>143</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>144</v>
+      <c r="A7" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="25" t="s">
-        <v>145</v>
-      </c>
-      <c r="B8" s="25" t="s">
-        <v>146</v>
+      <c r="A8" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="25" t="s">
-        <v>147</v>
-      </c>
-      <c r="B9" s="25" t="s">
-        <v>148</v>
+      <c r="A9" s="26" t="s">
+        <v>163</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="B10" s="25" t="s">
-        <v>150</v>
+      <c r="A10" s="26" t="s">
+        <v>165</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="B11" s="25" t="s">
-        <v>152</v>
+      <c r="A11" s="26" t="s">
+        <v>167</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>
